--- a/ch_03_getting_started_advanced_analysis/ch_03_mpg.xlsx
+++ b/ch_03_getting_started_advanced_analysis/ch_03_mpg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29809"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\AI-Powered-Analytics-in-Excel\ch-3-get-started-advanced-analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\AI-Powered-Analytics-in-Excel\ch_03_getting_started_advanced_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289980E9-4700-4551-8D2A-466FFAF2FDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4199CF7A-C67B-455C-9C9A-57A0E5EC2610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{DE2FC6D0-B278-4A6A-8CDE-4A3419D8176F}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="11">
   <si>
     <t>mpg</t>
   </si>
@@ -79,931 +79,13 @@
     <t>origin</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>usa</t>
-  </si>
-  <si>
-    <t>chevrolet chevelle malibu</t>
-  </si>
-  <si>
-    <t>buick skylark 320</t>
-  </si>
-  <si>
-    <t>plymouth satellite</t>
-  </si>
-  <si>
-    <t>amc rebel sst</t>
-  </si>
-  <si>
-    <t>ford torino</t>
-  </si>
-  <si>
-    <t>ford galaxie 500</t>
-  </si>
-  <si>
-    <t>chevrolet impala</t>
-  </si>
-  <si>
-    <t>plymouth fury iii</t>
-  </si>
-  <si>
-    <t>pontiac catalina</t>
-  </si>
-  <si>
-    <t>amc ambassador dpl</t>
-  </si>
-  <si>
-    <t>dodge challenger se</t>
-  </si>
-  <si>
-    <t>plymouth 'cuda 340</t>
-  </si>
-  <si>
-    <t>chevrolet monte carlo</t>
-  </si>
-  <si>
-    <t>buick estate wagon (sw)</t>
   </si>
   <si>
     <t>japan</t>
   </si>
   <si>
-    <t>toyota corona mark ii</t>
-  </si>
-  <si>
-    <t>plymouth duster</t>
-  </si>
-  <si>
-    <t>amc hornet</t>
-  </si>
-  <si>
-    <t>ford maverick</t>
-  </si>
-  <si>
-    <t>datsun pl510</t>
-  </si>
-  <si>
     <t>europe</t>
-  </si>
-  <si>
-    <t>volkswagen 1131 deluxe sedan</t>
-  </si>
-  <si>
-    <t>peugeot 504</t>
-  </si>
-  <si>
-    <t>audi 100 ls</t>
-  </si>
-  <si>
-    <t>saab 99e</t>
-  </si>
-  <si>
-    <t>bmw 2002</t>
-  </si>
-  <si>
-    <t>amc gremlin</t>
-  </si>
-  <si>
-    <t>ford f250</t>
-  </si>
-  <si>
-    <t>chevy c20</t>
-  </si>
-  <si>
-    <t>dodge d200</t>
-  </si>
-  <si>
-    <t>hi 1200d</t>
-  </si>
-  <si>
-    <t>chevrolet vega 2300</t>
-  </si>
-  <si>
-    <t>toyota corona</t>
-  </si>
-  <si>
-    <t>ford pinto</t>
-  </si>
-  <si>
-    <t>plymouth satellite custom</t>
-  </si>
-  <si>
-    <t>ford torino 500</t>
-  </si>
-  <si>
-    <t>amc matador</t>
-  </si>
-  <si>
-    <t>pontiac catalina brougham</t>
-  </si>
-  <si>
-    <t>dodge monaco (sw)</t>
-  </si>
-  <si>
-    <t>ford country squire (sw)</t>
-  </si>
-  <si>
-    <t>pontiac safari (sw)</t>
-  </si>
-  <si>
-    <t>amc hornet sportabout (sw)</t>
-  </si>
-  <si>
-    <t>chevrolet vega (sw)</t>
-  </si>
-  <si>
-    <t>pontiac firebird</t>
-  </si>
-  <si>
-    <t>ford mustang</t>
-  </si>
-  <si>
-    <t>mercury capri 2000</t>
-  </si>
-  <si>
-    <t>opel 1900</t>
-  </si>
-  <si>
-    <t>peugeot 304</t>
-  </si>
-  <si>
-    <t>fiat 124b</t>
-  </si>
-  <si>
-    <t>toyota corolla 1200</t>
-  </si>
-  <si>
-    <t>datsun 1200</t>
-  </si>
-  <si>
-    <t>volkswagen model 111</t>
-  </si>
-  <si>
-    <t>plymouth cricket</t>
-  </si>
-  <si>
-    <t>toyota corona hardtop</t>
-  </si>
-  <si>
-    <t>dodge colt hardtop</t>
-  </si>
-  <si>
-    <t>volkswagen type 3</t>
-  </si>
-  <si>
-    <t>chevrolet vega</t>
-  </si>
-  <si>
-    <t>ford pinto runabout</t>
-  </si>
-  <si>
-    <t>amc ambassador sst</t>
-  </si>
-  <si>
-    <t>mercury marquis</t>
-  </si>
-  <si>
-    <t>buick lesabre custom</t>
-  </si>
-  <si>
-    <t>oldsmobile delta 88 royale</t>
-  </si>
-  <si>
-    <t>chrysler newport royal</t>
-  </si>
-  <si>
-    <t>mazda rx2 coupe</t>
-  </si>
-  <si>
-    <t>amc matador (sw)</t>
-  </si>
-  <si>
-    <t>chevrolet chevelle concours (sw)</t>
-  </si>
-  <si>
-    <t>ford gran torino (sw)</t>
-  </si>
-  <si>
-    <t>plymouth satellite custom (sw)</t>
-  </si>
-  <si>
-    <t>volvo 145e (sw)</t>
-  </si>
-  <si>
-    <t>volkswagen 411 (sw)</t>
-  </si>
-  <si>
-    <t>peugeot 504 (sw)</t>
-  </si>
-  <si>
-    <t>renault 12 (sw)</t>
-  </si>
-  <si>
-    <t>ford pinto (sw)</t>
-  </si>
-  <si>
-    <t>datsun 510 (sw)</t>
-  </si>
-  <si>
-    <t>toyouta corona mark ii (sw)</t>
-  </si>
-  <si>
-    <t>dodge colt (sw)</t>
-  </si>
-  <si>
-    <t>toyota corolla 1600 (sw)</t>
-  </si>
-  <si>
-    <t>buick century 350</t>
-  </si>
-  <si>
-    <t>chevrolet malibu</t>
-  </si>
-  <si>
-    <t>ford gran torino</t>
-  </si>
-  <si>
-    <t>dodge coronet custom</t>
-  </si>
-  <si>
-    <t>mercury marquis brougham</t>
-  </si>
-  <si>
-    <t>chevrolet caprice classic</t>
-  </si>
-  <si>
-    <t>ford ltd</t>
-  </si>
-  <si>
-    <t>plymouth fury gran sedan</t>
-  </si>
-  <si>
-    <t>chrysler new yorker brougham</t>
-  </si>
-  <si>
-    <t>buick electra 225 custom</t>
-  </si>
-  <si>
-    <t>amc ambassador brougham</t>
-  </si>
-  <si>
-    <t>plymouth valiant</t>
-  </si>
-  <si>
-    <t>chevrolet nova custom</t>
-  </si>
-  <si>
-    <t>volkswagen super beetle</t>
-  </si>
-  <si>
-    <t>ford country</t>
-  </si>
-  <si>
-    <t>plymouth custom suburb</t>
-  </si>
-  <si>
-    <t>oldsmobile vista cruiser</t>
-  </si>
-  <si>
-    <t>toyota carina</t>
-  </si>
-  <si>
-    <t>datsun 610</t>
-  </si>
-  <si>
-    <t>maxda rx3</t>
-  </si>
-  <si>
-    <t>mercury capri v6</t>
-  </si>
-  <si>
-    <t>fiat 124 sport coupe</t>
-  </si>
-  <si>
-    <t>chevrolet monte carlo s</t>
-  </si>
-  <si>
-    <t>pontiac grand prix</t>
-  </si>
-  <si>
-    <t>fiat 128</t>
-  </si>
-  <si>
-    <t>opel manta</t>
-  </si>
-  <si>
-    <t>audi 100ls</t>
-  </si>
-  <si>
-    <t>volvo 144ea</t>
-  </si>
-  <si>
-    <t>dodge dart custom</t>
-  </si>
-  <si>
-    <t>saab 99le</t>
-  </si>
-  <si>
-    <t>toyota mark ii</t>
-  </si>
-  <si>
-    <t>oldsmobile omega</t>
-  </si>
-  <si>
-    <t>chevrolet nova</t>
-  </si>
-  <si>
-    <t>datsun b210</t>
-  </si>
-  <si>
-    <t>chevrolet chevelle malibu classic</t>
-  </si>
-  <si>
-    <t>plymouth satellite sebring</t>
-  </si>
-  <si>
-    <t>buick century luxus (sw)</t>
-  </si>
-  <si>
-    <t>dodge coronet custom (sw)</t>
-  </si>
-  <si>
-    <t>audi fox</t>
-  </si>
-  <si>
-    <t>volkswagen dasher</t>
-  </si>
-  <si>
-    <t>datsun 710</t>
-  </si>
-  <si>
-    <t>dodge colt</t>
-  </si>
-  <si>
-    <t>fiat 124 tc</t>
-  </si>
-  <si>
-    <t>honda civic</t>
-  </si>
-  <si>
-    <t>subaru</t>
-  </si>
-  <si>
-    <t>fiat x1.9</t>
-  </si>
-  <si>
-    <t>plymouth valiant custom</t>
-  </si>
-  <si>
-    <t>mercury monarch</t>
-  </si>
-  <si>
-    <t>chevrolet bel air</t>
-  </si>
-  <si>
-    <t>plymouth grand fury</t>
-  </si>
-  <si>
-    <t>buick century</t>
-  </si>
-  <si>
-    <t>chevroelt chevelle malibu</t>
-  </si>
-  <si>
-    <t>plymouth fury</t>
-  </si>
-  <si>
-    <t>buick skyhawk</t>
-  </si>
-  <si>
-    <t>chevrolet monza 2+2</t>
-  </si>
-  <si>
-    <t>ford mustang ii</t>
-  </si>
-  <si>
-    <t>toyota corolla</t>
-  </si>
-  <si>
-    <t>pontiac astro</t>
-  </si>
-  <si>
-    <t>volkswagen rabbit</t>
-  </si>
-  <si>
-    <t>amc pacer</t>
-  </si>
-  <si>
-    <t>volvo 244dl</t>
-  </si>
-  <si>
-    <t>honda civic cvcc</t>
-  </si>
-  <si>
-    <t>fiat 131</t>
-  </si>
-  <si>
-    <t>capri ii</t>
-  </si>
-  <si>
-    <t>renault 12tl</t>
-  </si>
-  <si>
-    <t>dodge coronet brougham</t>
-  </si>
-  <si>
-    <t>chevrolet chevette</t>
-  </si>
-  <si>
-    <t>chevrolet woody</t>
-  </si>
-  <si>
-    <t>vw rabbit</t>
-  </si>
-  <si>
-    <t>dodge aspen se</t>
-  </si>
-  <si>
-    <t>ford granada ghia</t>
-  </si>
-  <si>
-    <t>pontiac ventura sj</t>
-  </si>
-  <si>
-    <t>amc pacer d/l</t>
-  </si>
-  <si>
-    <t>datsun b-210</t>
-  </si>
-  <si>
-    <t>volvo 245</t>
-  </si>
-  <si>
-    <t>plymouth volare premier v8</t>
-  </si>
-  <si>
-    <t>mercedes-benz 280s</t>
-  </si>
-  <si>
-    <t>cadillac seville</t>
-  </si>
-  <si>
-    <t>chevy c10</t>
-  </si>
-  <si>
-    <t>ford f108</t>
-  </si>
-  <si>
-    <t>dodge d100</t>
-  </si>
-  <si>
-    <t>honda accord cvcc</t>
-  </si>
-  <si>
-    <t>buick opel isuzu deluxe</t>
-  </si>
-  <si>
-    <t>renault 5 gtl</t>
-  </si>
-  <si>
-    <t>plymouth arrow gs</t>
-  </si>
-  <si>
-    <t>datsun f-10 hatchback</t>
-  </si>
-  <si>
-    <t>oldsmobile cutlass supreme</t>
-  </si>
-  <si>
-    <t>dodge monaco brougham</t>
-  </si>
-  <si>
-    <t>mercury cougar brougham</t>
-  </si>
-  <si>
-    <t>chevrolet concours</t>
-  </si>
-  <si>
-    <t>buick skylark</t>
-  </si>
-  <si>
-    <t>plymouth volare custom</t>
-  </si>
-  <si>
-    <t>ford granada</t>
-  </si>
-  <si>
-    <t>pontiac grand prix lj</t>
-  </si>
-  <si>
-    <t>chevrolet monte carlo landau</t>
-  </si>
-  <si>
-    <t>chrysler cordoba</t>
-  </si>
-  <si>
-    <t>ford thunderbird</t>
-  </si>
-  <si>
-    <t>volkswagen rabbit custom</t>
-  </si>
-  <si>
-    <t>pontiac sunbird coupe</t>
-  </si>
-  <si>
-    <t>toyota corolla liftback</t>
-  </si>
-  <si>
-    <t>ford mustang ii 2+2</t>
-  </si>
-  <si>
-    <t>dodge colt m/m</t>
-  </si>
-  <si>
-    <t>subaru dl</t>
-  </si>
-  <si>
-    <t>datsun 810</t>
-  </si>
-  <si>
-    <t>bmw 320i</t>
-  </si>
-  <si>
-    <t>mazda rx-4</t>
-  </si>
-  <si>
-    <t>volkswagen rabbit custom diesel</t>
-  </si>
-  <si>
-    <t>ford fiesta</t>
-  </si>
-  <si>
-    <t>mazda glc deluxe</t>
-  </si>
-  <si>
-    <t>datsun b210 gx</t>
-  </si>
-  <si>
-    <t>oldsmobile cutlass salon brougham</t>
-  </si>
-  <si>
-    <t>dodge diplomat</t>
-  </si>
-  <si>
-    <t>mercury monarch ghia</t>
-  </si>
-  <si>
-    <t>pontiac phoenix lj</t>
-  </si>
-  <si>
-    <t>ford fairmont (auto)</t>
-  </si>
-  <si>
-    <t>ford fairmont (man)</t>
-  </si>
-  <si>
-    <t>plymouth volare</t>
-  </si>
-  <si>
-    <t>amc concord</t>
-  </si>
-  <si>
-    <t>buick century special</t>
-  </si>
-  <si>
-    <t>mercury zephyr</t>
-  </si>
-  <si>
-    <t>dodge aspen</t>
-  </si>
-  <si>
-    <t>amc concord d/l</t>
-  </si>
-  <si>
-    <t>buick regal sport coupe (turbo)</t>
-  </si>
-  <si>
-    <t>ford futura</t>
-  </si>
-  <si>
-    <t>dodge magnum xe</t>
-  </si>
-  <si>
-    <t>datsun 510</t>
-  </si>
-  <si>
-    <t>dodge omni</t>
-  </si>
-  <si>
-    <t>toyota celica gt liftback</t>
-  </si>
-  <si>
-    <t>plymouth sapporo</t>
-  </si>
-  <si>
-    <t>oldsmobile starfire sx</t>
-  </si>
-  <si>
-    <t>datsun 200-sx</t>
-  </si>
-  <si>
-    <t>audi 5000</t>
-  </si>
-  <si>
-    <t>volvo 264gl</t>
-  </si>
-  <si>
-    <t>saab 99gle</t>
-  </si>
-  <si>
-    <t>peugeot 604sl</t>
-  </si>
-  <si>
-    <t>volkswagen scirocco</t>
-  </si>
-  <si>
-    <t>honda accord lx</t>
-  </si>
-  <si>
-    <t>pontiac lemans v6</t>
-  </si>
-  <si>
-    <t>mercury zephyr 6</t>
-  </si>
-  <si>
-    <t>ford fairmont 4</t>
-  </si>
-  <si>
-    <t>amc concord dl 6</t>
-  </si>
-  <si>
-    <t>dodge aspen 6</t>
-  </si>
-  <si>
-    <t>ford ltd landau</t>
-  </si>
-  <si>
-    <t>mercury grand marquis</t>
-  </si>
-  <si>
-    <t>dodge st. regis</t>
-  </si>
-  <si>
-    <t>chevrolet malibu classic (sw)</t>
-  </si>
-  <si>
-    <t>chrysler lebaron town @ country (sw)</t>
-  </si>
-  <si>
-    <t>vw rabbit custom</t>
-  </si>
-  <si>
-    <t>maxda glc deluxe</t>
-  </si>
-  <si>
-    <t>dodge colt hatchback custom</t>
-  </si>
-  <si>
-    <t>amc spirit dl</t>
-  </si>
-  <si>
-    <t>mercedes benz 300d</t>
-  </si>
-  <si>
-    <t>cadillac eldorado</t>
-  </si>
-  <si>
-    <t>plymouth horizon</t>
-  </si>
-  <si>
-    <t>plymouth horizon tc3</t>
-  </si>
-  <si>
-    <t>datsun 210</t>
-  </si>
-  <si>
-    <t>fiat strada custom</t>
-  </si>
-  <si>
-    <t>buick skylark limited</t>
-  </si>
-  <si>
-    <t>chevrolet citation</t>
-  </si>
-  <si>
-    <t>oldsmobile omega brougham</t>
-  </si>
-  <si>
-    <t>pontiac phoenix</t>
-  </si>
-  <si>
-    <t>toyota corolla tercel</t>
-  </si>
-  <si>
-    <t>datsun 310</t>
-  </si>
-  <si>
-    <t>ford fairmont</t>
-  </si>
-  <si>
-    <t>audi 4000</t>
-  </si>
-  <si>
-    <t>toyota corona liftback</t>
-  </si>
-  <si>
-    <t>mazda 626</t>
-  </si>
-  <si>
-    <t>datsun 510 hatchback</t>
-  </si>
-  <si>
-    <t>mazda glc</t>
-  </si>
-  <si>
-    <t>vw rabbit c (diesel)</t>
-  </si>
-  <si>
-    <t>vw dasher (diesel)</t>
-  </si>
-  <si>
-    <t>audi 5000s (diesel)</t>
-  </si>
-  <si>
-    <t>mercedes-benz 240d</t>
-  </si>
-  <si>
-    <t>honda civic 1500 gl</t>
-  </si>
-  <si>
-    <t>renault lecar deluxe</t>
-  </si>
-  <si>
-    <t>vokswagen rabbit</t>
-  </si>
-  <si>
-    <t>datsun 280-zx</t>
-  </si>
-  <si>
-    <t>mazda rx-7 gs</t>
-  </si>
-  <si>
-    <t>triumph tr7 coupe</t>
-  </si>
-  <si>
-    <t>ford mustang cobra</t>
-  </si>
-  <si>
-    <t>honda accord</t>
-  </si>
-  <si>
-    <t>plymouth reliant</t>
-  </si>
-  <si>
-    <t>dodge aries wagon (sw)</t>
-  </si>
-  <si>
-    <t>toyota starlet</t>
-  </si>
-  <si>
-    <t>plymouth champ</t>
-  </si>
-  <si>
-    <t>honda civic 1300</t>
-  </si>
-  <si>
-    <t>datsun 210 mpg</t>
-  </si>
-  <si>
-    <t>toyota tercel</t>
-  </si>
-  <si>
-    <t>mazda glc 4</t>
-  </si>
-  <si>
-    <t>plymouth horizon 4</t>
-  </si>
-  <si>
-    <t>ford escort 4w</t>
-  </si>
-  <si>
-    <t>ford escort 2h</t>
-  </si>
-  <si>
-    <t>volkswagen jetta</t>
-  </si>
-  <si>
-    <t>renault 18i</t>
-  </si>
-  <si>
-    <t>honda prelude</t>
-  </si>
-  <si>
-    <t>datsun 200sx</t>
-  </si>
-  <si>
-    <t>peugeot 505s turbo diesel</t>
-  </si>
-  <si>
-    <t>volvo diesel</t>
-  </si>
-  <si>
-    <t>toyota cressida</t>
-  </si>
-  <si>
-    <t>datsun 810 maxima</t>
-  </si>
-  <si>
-    <t>oldsmobile cutlass ls</t>
-  </si>
-  <si>
-    <t>ford granada gl</t>
-  </si>
-  <si>
-    <t>chrysler lebaron salon</t>
-  </si>
-  <si>
-    <t>chevrolet cavalier</t>
-  </si>
-  <si>
-    <t>chevrolet cavalier wagon</t>
-  </si>
-  <si>
-    <t>chevrolet cavalier 2-door</t>
-  </si>
-  <si>
-    <t>pontiac j2000 se hatchback</t>
-  </si>
-  <si>
-    <t>dodge aries se</t>
-  </si>
-  <si>
-    <t>ford fairmont futura</t>
-  </si>
-  <si>
-    <t>amc concord dl</t>
-  </si>
-  <si>
-    <t>volkswagen rabbit l</t>
-  </si>
-  <si>
-    <t>mazda glc custom l</t>
-  </si>
-  <si>
-    <t>mazda glc custom</t>
-  </si>
-  <si>
-    <t>plymouth horizon miser</t>
-  </si>
-  <si>
-    <t>mercury lynx l</t>
-  </si>
-  <si>
-    <t>nissan stanza xe</t>
-  </si>
-  <si>
-    <t>honda civic (auto)</t>
-  </si>
-  <si>
-    <t>datsun 310 gx</t>
-  </si>
-  <si>
-    <t>buick century limited</t>
-  </si>
-  <si>
-    <t>oldsmobile cutlass ciera (diesel)</t>
-  </si>
-  <si>
-    <t>chrysler lebaron medallion</t>
-  </si>
-  <si>
-    <t>ford granada l</t>
-  </si>
-  <si>
-    <t>toyota celica gt</t>
-  </si>
-  <si>
-    <t>dodge charger 2.2</t>
-  </si>
-  <si>
-    <t>chevrolet camaro</t>
-  </si>
-  <si>
-    <t>ford mustang gl</t>
-  </si>
-  <si>
-    <t>vw pickup</t>
-  </si>
-  <si>
-    <t>dodge rampage</t>
-  </si>
-  <si>
-    <t>ford ranger</t>
-  </si>
-  <si>
-    <t>chevy s-10</t>
   </si>
 </sst>
 </file>
@@ -1557,9 +639,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C49E5C8-DD4E-4057-90A7-3F9DE6DB3CA7}" name="autompg" displayName="autompg" ref="A1:I399" totalsRowShown="0">
-  <autoFilter ref="A1:I399" xr:uid="{2C49E5C8-DD4E-4057-90A7-3F9DE6DB3CA7}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C49E5C8-DD4E-4057-90A7-3F9DE6DB3CA7}" name="autompg" displayName="autompg" ref="A1:H399" totalsRowShown="0">
+  <autoFilter ref="A1:H399" xr:uid="{2C49E5C8-DD4E-4057-90A7-3F9DE6DB3CA7}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{4A5053B5-BF8B-432A-8BD6-DAA0BC41D435}" name="mpg"/>
     <tableColumn id="2" xr3:uid="{114036D8-06F0-453B-A613-2CB59F652FE7}" name="cylinders"/>
     <tableColumn id="3" xr3:uid="{AB637BE5-22EC-4217-9557-254002515A57}" name="displacement"/>
@@ -1568,7 +650,6 @@
     <tableColumn id="6" xr3:uid="{0B770894-3911-496A-BBBF-C76267FC7232}" name="acceleration"/>
     <tableColumn id="7" xr3:uid="{B57FCA86-E16F-4BED-B901-917E7E12EDAD}" name="model_year"/>
     <tableColumn id="8" xr3:uid="{EF6E5C53-55C4-4FFA-A7FB-DCF83C3CA469}" name="origin"/>
-    <tableColumn id="9" xr3:uid="{B5F1B161-C1DB-4052-AD4B-7317D4BAC64E}" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1891,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E6936C-FA72-492B-8F57-08DF00678A65}">
-  <dimension ref="A1:I399"/>
+  <dimension ref="A1:H399"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="2" max="2" width="9.2578125" customWidth="1"/>
@@ -1901,7 +982,7 @@
     <col min="7" max="7" width="11.2578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1926,11 +1007,8 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.85">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A2">
         <v>18</v>
       </c>
@@ -1953,13 +1031,10 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A3">
         <v>15</v>
       </c>
@@ -1982,13 +1057,10 @@
         <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2011,13 +1083,10 @@
         <v>70</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A5">
         <v>16</v>
       </c>
@@ -2040,13 +1109,10 @@
         <v>70</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A6">
         <v>17</v>
       </c>
@@ -2069,13 +1135,10 @@
         <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A7">
         <v>15</v>
       </c>
@@ -2098,13 +1161,10 @@
         <v>70</v>
       </c>
       <c r="H7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2127,13 +1187,10 @@
         <v>70</v>
       </c>
       <c r="H8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2156,13 +1213,10 @@
         <v>70</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2185,13 +1239,10 @@
         <v>70</v>
       </c>
       <c r="H10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A11">
         <v>15</v>
       </c>
@@ -2214,13 +1265,10 @@
         <v>70</v>
       </c>
       <c r="H11" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A12">
         <v>15</v>
       </c>
@@ -2243,13 +1291,10 @@
         <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A13">
         <v>14</v>
       </c>
@@ -2272,13 +1317,10 @@
         <v>70</v>
       </c>
       <c r="H13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A14">
         <v>15</v>
       </c>
@@ -2301,13 +1343,10 @@
         <v>70</v>
       </c>
       <c r="H14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2330,13 +1369,10 @@
         <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A16">
         <v>24</v>
       </c>
@@ -2359,13 +1395,10 @@
         <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A17">
         <v>22</v>
       </c>
@@ -2388,13 +1421,10 @@
         <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A18">
         <v>18</v>
       </c>
@@ -2417,13 +1447,10 @@
         <v>70</v>
       </c>
       <c r="H18" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A19">
         <v>21</v>
       </c>
@@ -2446,13 +1473,10 @@
         <v>70</v>
       </c>
       <c r="H19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A20">
         <v>27</v>
       </c>
@@ -2475,13 +1499,10 @@
         <v>70</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A21">
         <v>26</v>
       </c>
@@ -2504,13 +1525,10 @@
         <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A22">
         <v>25</v>
       </c>
@@ -2533,13 +1551,10 @@
         <v>70</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A23">
         <v>24</v>
       </c>
@@ -2562,13 +1577,10 @@
         <v>70</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A24">
         <v>25</v>
       </c>
@@ -2591,13 +1603,10 @@
         <v>70</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A25">
         <v>26</v>
       </c>
@@ -2620,13 +1629,10 @@
         <v>70</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A26">
         <v>21</v>
       </c>
@@ -2649,13 +1655,10 @@
         <v>70</v>
       </c>
       <c r="H26" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2678,13 +1681,10 @@
         <v>70</v>
       </c>
       <c r="H27" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2707,13 +1707,10 @@
         <v>70</v>
       </c>
       <c r="H28" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A29">
         <v>11</v>
       </c>
@@ -2736,13 +1733,10 @@
         <v>70</v>
       </c>
       <c r="H29" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A30">
         <v>9</v>
       </c>
@@ -2765,13 +1759,10 @@
         <v>70</v>
       </c>
       <c r="H30" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2794,13 +1785,10 @@
         <v>71</v>
       </c>
       <c r="H31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2823,13 +1811,10 @@
         <v>71</v>
       </c>
       <c r="H32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A33">
         <v>25</v>
       </c>
@@ -2852,13 +1837,10 @@
         <v>71</v>
       </c>
       <c r="H33" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A34">
         <v>25</v>
       </c>
@@ -2878,13 +1860,10 @@
         <v>71</v>
       </c>
       <c r="H34" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A35">
         <v>19</v>
       </c>
@@ -2907,13 +1886,10 @@
         <v>71</v>
       </c>
       <c r="H35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A36">
         <v>16</v>
       </c>
@@ -2936,13 +1912,10 @@
         <v>71</v>
       </c>
       <c r="H36" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A37">
         <v>17</v>
       </c>
@@ -2965,13 +1938,10 @@
         <v>71</v>
       </c>
       <c r="H37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A38">
         <v>19</v>
       </c>
@@ -2994,13 +1964,10 @@
         <v>71</v>
       </c>
       <c r="H38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A39">
         <v>18</v>
       </c>
@@ -3023,13 +1990,10 @@
         <v>71</v>
       </c>
       <c r="H39" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A40">
         <v>14</v>
       </c>
@@ -3052,13 +2016,10 @@
         <v>71</v>
       </c>
       <c r="H40" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A41">
         <v>14</v>
       </c>
@@ -3081,13 +2042,10 @@
         <v>71</v>
       </c>
       <c r="H41" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A42">
         <v>14</v>
       </c>
@@ -3110,13 +2068,10 @@
         <v>71</v>
       </c>
       <c r="H42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A43">
         <v>14</v>
       </c>
@@ -3139,13 +2094,10 @@
         <v>71</v>
       </c>
       <c r="H43" t="s">
-        <v>9</v>
-      </c>
-      <c r="I43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A44">
         <v>12</v>
       </c>
@@ -3168,13 +2120,10 @@
         <v>71</v>
       </c>
       <c r="H44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A45">
         <v>13</v>
       </c>
@@ -3197,13 +2146,10 @@
         <v>71</v>
       </c>
       <c r="H45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A46">
         <v>13</v>
       </c>
@@ -3226,13 +2172,10 @@
         <v>71</v>
       </c>
       <c r="H46" t="s">
-        <v>9</v>
-      </c>
-      <c r="I46" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A47">
         <v>18</v>
       </c>
@@ -3255,13 +2198,10 @@
         <v>71</v>
       </c>
       <c r="H47" t="s">
-        <v>9</v>
-      </c>
-      <c r="I47" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A48">
         <v>22</v>
       </c>
@@ -3284,13 +2224,10 @@
         <v>71</v>
       </c>
       <c r="H48" t="s">
-        <v>9</v>
-      </c>
-      <c r="I48" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A49">
         <v>19</v>
       </c>
@@ -3313,13 +2250,10 @@
         <v>71</v>
       </c>
       <c r="H49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A50">
         <v>18</v>
       </c>
@@ -3342,13 +2276,10 @@
         <v>71</v>
       </c>
       <c r="H50" t="s">
-        <v>9</v>
-      </c>
-      <c r="I50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A51">
         <v>23</v>
       </c>
@@ -3371,13 +2302,10 @@
         <v>71</v>
       </c>
       <c r="H51" t="s">
-        <v>9</v>
-      </c>
-      <c r="I51" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A52">
         <v>28</v>
       </c>
@@ -3400,13 +2328,10 @@
         <v>71</v>
       </c>
       <c r="H52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A53">
         <v>30</v>
       </c>
@@ -3429,13 +2354,10 @@
         <v>71</v>
       </c>
       <c r="H53" t="s">
-        <v>30</v>
-      </c>
-      <c r="I53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A54">
         <v>30</v>
       </c>
@@ -3458,13 +2380,10 @@
         <v>71</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A55">
         <v>31</v>
       </c>
@@ -3487,13 +2406,10 @@
         <v>71</v>
       </c>
       <c r="H55" t="s">
-        <v>24</v>
-      </c>
-      <c r="I55" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A56">
         <v>35</v>
       </c>
@@ -3516,13 +2432,10 @@
         <v>71</v>
       </c>
       <c r="H56" t="s">
-        <v>24</v>
-      </c>
-      <c r="I56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A57">
         <v>27</v>
       </c>
@@ -3545,13 +2458,10 @@
         <v>71</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
-      </c>
-      <c r="I57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A58">
         <v>26</v>
       </c>
@@ -3574,13 +2484,10 @@
         <v>71</v>
       </c>
       <c r="H58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A59">
         <v>24</v>
       </c>
@@ -3603,13 +2510,10 @@
         <v>72</v>
       </c>
       <c r="H59" t="s">
-        <v>24</v>
-      </c>
-      <c r="I59" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A60">
         <v>25</v>
       </c>
@@ -3632,13 +2536,10 @@
         <v>72</v>
       </c>
       <c r="H60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A61">
         <v>23</v>
       </c>
@@ -3661,13 +2562,10 @@
         <v>72</v>
       </c>
       <c r="H61" t="s">
-        <v>30</v>
-      </c>
-      <c r="I61" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A62">
         <v>20</v>
       </c>
@@ -3690,13 +2588,10 @@
         <v>72</v>
       </c>
       <c r="H62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A63">
         <v>21</v>
       </c>
@@ -3719,13 +2614,10 @@
         <v>72</v>
       </c>
       <c r="H63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I63" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A64">
         <v>13</v>
       </c>
@@ -3748,13 +2640,10 @@
         <v>72</v>
       </c>
       <c r="H64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I64" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A65">
         <v>14</v>
       </c>
@@ -3777,13 +2666,10 @@
         <v>72</v>
       </c>
       <c r="H65" t="s">
-        <v>9</v>
-      </c>
-      <c r="I65" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A66">
         <v>15</v>
       </c>
@@ -3806,13 +2692,10 @@
         <v>72</v>
       </c>
       <c r="H66" t="s">
-        <v>9</v>
-      </c>
-      <c r="I66" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A67">
         <v>14</v>
       </c>
@@ -3835,13 +2718,10 @@
         <v>72</v>
       </c>
       <c r="H67" t="s">
-        <v>9</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A68">
         <v>17</v>
       </c>
@@ -3864,13 +2744,10 @@
         <v>72</v>
       </c>
       <c r="H68" t="s">
-        <v>9</v>
-      </c>
-      <c r="I68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A69">
         <v>11</v>
       </c>
@@ -3893,13 +2770,10 @@
         <v>72</v>
       </c>
       <c r="H69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I69" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A70">
         <v>13</v>
       </c>
@@ -3922,13 +2796,10 @@
         <v>72</v>
       </c>
       <c r="H70" t="s">
-        <v>9</v>
-      </c>
-      <c r="I70" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A71">
         <v>12</v>
       </c>
@@ -3951,13 +2822,10 @@
         <v>72</v>
       </c>
       <c r="H71" t="s">
-        <v>9</v>
-      </c>
-      <c r="I71" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A72">
         <v>13</v>
       </c>
@@ -3980,13 +2848,10 @@
         <v>72</v>
       </c>
       <c r="H72" t="s">
-        <v>9</v>
-      </c>
-      <c r="I72" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A73">
         <v>19</v>
       </c>
@@ -4009,13 +2874,10 @@
         <v>72</v>
       </c>
       <c r="H73" t="s">
-        <v>24</v>
-      </c>
-      <c r="I73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A74">
         <v>15</v>
       </c>
@@ -4038,13 +2900,10 @@
         <v>72</v>
       </c>
       <c r="H74" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A75">
         <v>13</v>
       </c>
@@ -4067,13 +2926,10 @@
         <v>72</v>
       </c>
       <c r="H75" t="s">
-        <v>9</v>
-      </c>
-      <c r="I75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A76">
         <v>13</v>
       </c>
@@ -4096,13 +2952,10 @@
         <v>72</v>
       </c>
       <c r="H76" t="s">
-        <v>9</v>
-      </c>
-      <c r="I76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A77">
         <v>14</v>
       </c>
@@ -4125,13 +2978,10 @@
         <v>72</v>
       </c>
       <c r="H77" t="s">
-        <v>9</v>
-      </c>
-      <c r="I77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A78">
         <v>18</v>
       </c>
@@ -4154,13 +3004,10 @@
         <v>72</v>
       </c>
       <c r="H78" t="s">
-        <v>30</v>
-      </c>
-      <c r="I78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A79">
         <v>22</v>
       </c>
@@ -4183,13 +3030,10 @@
         <v>72</v>
       </c>
       <c r="H79" t="s">
-        <v>30</v>
-      </c>
-      <c r="I79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A80">
         <v>21</v>
       </c>
@@ -4212,13 +3056,10 @@
         <v>72</v>
       </c>
       <c r="H80" t="s">
-        <v>30</v>
-      </c>
-      <c r="I80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A81">
         <v>26</v>
       </c>
@@ -4241,13 +3082,10 @@
         <v>72</v>
       </c>
       <c r="H81" t="s">
-        <v>30</v>
-      </c>
-      <c r="I81" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A82">
         <v>22</v>
       </c>
@@ -4270,13 +3108,10 @@
         <v>72</v>
       </c>
       <c r="H82" t="s">
-        <v>9</v>
-      </c>
-      <c r="I82" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A83">
         <v>28</v>
       </c>
@@ -4299,13 +3134,10 @@
         <v>72</v>
       </c>
       <c r="H83" t="s">
-        <v>24</v>
-      </c>
-      <c r="I83" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A84">
         <v>23</v>
       </c>
@@ -4328,13 +3160,10 @@
         <v>72</v>
       </c>
       <c r="H84" t="s">
-        <v>24</v>
-      </c>
-      <c r="I84" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A85">
         <v>28</v>
       </c>
@@ -4357,13 +3186,10 @@
         <v>72</v>
       </c>
       <c r="H85" t="s">
-        <v>9</v>
-      </c>
-      <c r="I85" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A86">
         <v>27</v>
       </c>
@@ -4386,13 +3212,10 @@
         <v>72</v>
       </c>
       <c r="H86" t="s">
-        <v>24</v>
-      </c>
-      <c r="I86" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A87">
         <v>13</v>
       </c>
@@ -4415,13 +3238,10 @@
         <v>73</v>
       </c>
       <c r="H87" t="s">
-        <v>9</v>
-      </c>
-      <c r="I87" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A88">
         <v>14</v>
       </c>
@@ -4444,13 +3264,10 @@
         <v>73</v>
       </c>
       <c r="H88" t="s">
-        <v>9</v>
-      </c>
-      <c r="I88" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A89">
         <v>13</v>
       </c>
@@ -4473,13 +3290,10 @@
         <v>73</v>
       </c>
       <c r="H89" t="s">
-        <v>9</v>
-      </c>
-      <c r="I89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A90">
         <v>14</v>
       </c>
@@ -4502,13 +3316,10 @@
         <v>73</v>
       </c>
       <c r="H90" t="s">
-        <v>9</v>
-      </c>
-      <c r="I90" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A91">
         <v>15</v>
       </c>
@@ -4531,13 +3342,10 @@
         <v>73</v>
       </c>
       <c r="H91" t="s">
-        <v>9</v>
-      </c>
-      <c r="I91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A92">
         <v>12</v>
       </c>
@@ -4560,13 +3368,10 @@
         <v>73</v>
       </c>
       <c r="H92" t="s">
-        <v>9</v>
-      </c>
-      <c r="I92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A93">
         <v>13</v>
       </c>
@@ -4589,13 +3394,10 @@
         <v>73</v>
       </c>
       <c r="H93" t="s">
-        <v>9</v>
-      </c>
-      <c r="I93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A94">
         <v>13</v>
       </c>
@@ -4618,13 +3420,10 @@
         <v>73</v>
       </c>
       <c r="H94" t="s">
-        <v>9</v>
-      </c>
-      <c r="I94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A95">
         <v>14</v>
       </c>
@@ -4647,13 +3446,10 @@
         <v>73</v>
       </c>
       <c r="H95" t="s">
-        <v>9</v>
-      </c>
-      <c r="I95" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A96">
         <v>13</v>
       </c>
@@ -4676,13 +3472,10 @@
         <v>73</v>
       </c>
       <c r="H96" t="s">
-        <v>9</v>
-      </c>
-      <c r="I96" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4705,13 +3498,10 @@
         <v>73</v>
       </c>
       <c r="H97" t="s">
-        <v>9</v>
-      </c>
-      <c r="I97" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A98">
         <v>13</v>
       </c>
@@ -4734,13 +3524,10 @@
         <v>73</v>
       </c>
       <c r="H98" t="s">
-        <v>9</v>
-      </c>
-      <c r="I98" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A99">
         <v>18</v>
       </c>
@@ -4763,13 +3550,10 @@
         <v>73</v>
       </c>
       <c r="H99" t="s">
-        <v>9</v>
-      </c>
-      <c r="I99" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A100">
         <v>16</v>
       </c>
@@ -4792,13 +3576,10 @@
         <v>73</v>
       </c>
       <c r="H100" t="s">
-        <v>9</v>
-      </c>
-      <c r="I100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A101">
         <v>18</v>
       </c>
@@ -4821,13 +3602,10 @@
         <v>73</v>
       </c>
       <c r="H101" t="s">
-        <v>9</v>
-      </c>
-      <c r="I101" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A102">
         <v>18</v>
       </c>
@@ -4850,13 +3628,10 @@
         <v>73</v>
       </c>
       <c r="H102" t="s">
-        <v>9</v>
-      </c>
-      <c r="I102" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A103">
         <v>23</v>
       </c>
@@ -4879,13 +3654,10 @@
         <v>73</v>
       </c>
       <c r="H103" t="s">
-        <v>9</v>
-      </c>
-      <c r="I103" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A104">
         <v>26</v>
       </c>
@@ -4908,13 +3680,10 @@
         <v>73</v>
       </c>
       <c r="H104" t="s">
-        <v>30</v>
-      </c>
-      <c r="I104" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A105">
         <v>11</v>
       </c>
@@ -4937,13 +3706,10 @@
         <v>73</v>
       </c>
       <c r="H105" t="s">
-        <v>9</v>
-      </c>
-      <c r="I105" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A106">
         <v>12</v>
       </c>
@@ -4966,13 +3732,10 @@
         <v>73</v>
       </c>
       <c r="H106" t="s">
-        <v>9</v>
-      </c>
-      <c r="I106" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A107">
         <v>13</v>
       </c>
@@ -4995,13 +3758,10 @@
         <v>73</v>
       </c>
       <c r="H107" t="s">
-        <v>9</v>
-      </c>
-      <c r="I107" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A108">
         <v>12</v>
       </c>
@@ -5024,13 +3784,10 @@
         <v>73</v>
       </c>
       <c r="H108" t="s">
-        <v>9</v>
-      </c>
-      <c r="I108" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A109">
         <v>18</v>
       </c>
@@ -5053,13 +3810,10 @@
         <v>73</v>
       </c>
       <c r="H109" t="s">
-        <v>9</v>
-      </c>
-      <c r="I109" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A110">
         <v>20</v>
       </c>
@@ -5082,13 +3836,10 @@
         <v>73</v>
       </c>
       <c r="H110" t="s">
-        <v>24</v>
-      </c>
-      <c r="I110" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A111">
         <v>21</v>
       </c>
@@ -5111,13 +3862,10 @@
         <v>73</v>
       </c>
       <c r="H111" t="s">
-        <v>9</v>
-      </c>
-      <c r="I111" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A112">
         <v>22</v>
       </c>
@@ -5140,13 +3888,10 @@
         <v>73</v>
       </c>
       <c r="H112" t="s">
-        <v>24</v>
-      </c>
-      <c r="I112" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A113">
         <v>18</v>
       </c>
@@ -5169,13 +3914,10 @@
         <v>73</v>
       </c>
       <c r="H113" t="s">
-        <v>24</v>
-      </c>
-      <c r="I113" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A114">
         <v>19</v>
       </c>
@@ -5198,13 +3940,10 @@
         <v>73</v>
       </c>
       <c r="H114" t="s">
-        <v>9</v>
-      </c>
-      <c r="I114" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A115">
         <v>21</v>
       </c>
@@ -5227,13 +3966,10 @@
         <v>73</v>
       </c>
       <c r="H115" t="s">
-        <v>9</v>
-      </c>
-      <c r="I115" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A116">
         <v>26</v>
       </c>
@@ -5256,13 +3992,10 @@
         <v>73</v>
       </c>
       <c r="H116" t="s">
-        <v>30</v>
-      </c>
-      <c r="I116" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A117">
         <v>15</v>
       </c>
@@ -5285,13 +4018,10 @@
         <v>73</v>
       </c>
       <c r="H117" t="s">
-        <v>9</v>
-      </c>
-      <c r="I117" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A118">
         <v>16</v>
       </c>
@@ -5314,13 +4044,10 @@
         <v>73</v>
       </c>
       <c r="H118" t="s">
-        <v>9</v>
-      </c>
-      <c r="I118" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A119">
         <v>29</v>
       </c>
@@ -5343,13 +4070,10 @@
         <v>73</v>
       </c>
       <c r="H119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I119" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A120">
         <v>24</v>
       </c>
@@ -5372,13 +4096,10 @@
         <v>73</v>
       </c>
       <c r="H120" t="s">
-        <v>30</v>
-      </c>
-      <c r="I120" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A121">
         <v>20</v>
       </c>
@@ -5401,13 +4122,10 @@
         <v>73</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
-      </c>
-      <c r="I121" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A122">
         <v>19</v>
       </c>
@@ -5430,13 +4148,10 @@
         <v>73</v>
       </c>
       <c r="H122" t="s">
-        <v>30</v>
-      </c>
-      <c r="I122" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A123">
         <v>15</v>
       </c>
@@ -5459,13 +4174,10 @@
         <v>73</v>
       </c>
       <c r="H123" t="s">
-        <v>9</v>
-      </c>
-      <c r="I123" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A124">
         <v>24</v>
       </c>
@@ -5488,13 +4200,10 @@
         <v>73</v>
       </c>
       <c r="H124" t="s">
-        <v>30</v>
-      </c>
-      <c r="I124" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A125">
         <v>20</v>
       </c>
@@ -5517,13 +4226,10 @@
         <v>73</v>
       </c>
       <c r="H125" t="s">
-        <v>24</v>
-      </c>
-      <c r="I125" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A126">
         <v>11</v>
       </c>
@@ -5546,13 +4252,10 @@
         <v>73</v>
       </c>
       <c r="H126" t="s">
-        <v>9</v>
-      </c>
-      <c r="I126" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A127">
         <v>20</v>
       </c>
@@ -5575,13 +4278,10 @@
         <v>74</v>
       </c>
       <c r="H127" t="s">
-        <v>9</v>
-      </c>
-      <c r="I127" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A128">
         <v>21</v>
       </c>
@@ -5601,13 +4301,10 @@
         <v>74</v>
       </c>
       <c r="H128" t="s">
-        <v>9</v>
-      </c>
-      <c r="I128" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A129">
         <v>19</v>
       </c>
@@ -5630,13 +4327,10 @@
         <v>74</v>
       </c>
       <c r="H129" t="s">
-        <v>9</v>
-      </c>
-      <c r="I129" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A130">
         <v>15</v>
       </c>
@@ -5659,13 +4353,10 @@
         <v>74</v>
       </c>
       <c r="H130" t="s">
-        <v>9</v>
-      </c>
-      <c r="I130" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A131">
         <v>31</v>
       </c>
@@ -5688,13 +4379,10 @@
         <v>74</v>
       </c>
       <c r="H131" t="s">
-        <v>24</v>
-      </c>
-      <c r="I131" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A132">
         <v>26</v>
       </c>
@@ -5717,13 +4405,10 @@
         <v>74</v>
       </c>
       <c r="H132" t="s">
-        <v>9</v>
-      </c>
-      <c r="I132" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A133">
         <v>32</v>
       </c>
@@ -5746,13 +4431,10 @@
         <v>74</v>
       </c>
       <c r="H133" t="s">
-        <v>24</v>
-      </c>
-      <c r="I133" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A134">
         <v>25</v>
       </c>
@@ -5775,13 +4457,10 @@
         <v>74</v>
       </c>
       <c r="H134" t="s">
-        <v>9</v>
-      </c>
-      <c r="I134" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A135">
         <v>16</v>
       </c>
@@ -5804,13 +4483,10 @@
         <v>74</v>
       </c>
       <c r="H135" t="s">
-        <v>9</v>
-      </c>
-      <c r="I135" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A136">
         <v>16</v>
       </c>
@@ -5833,13 +4509,10 @@
         <v>74</v>
       </c>
       <c r="H136" t="s">
-        <v>9</v>
-      </c>
-      <c r="I136" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A137">
         <v>18</v>
       </c>
@@ -5862,13 +4535,10 @@
         <v>74</v>
       </c>
       <c r="H137" t="s">
-        <v>9</v>
-      </c>
-      <c r="I137" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A138">
         <v>16</v>
       </c>
@@ -5891,13 +4561,10 @@
         <v>74</v>
       </c>
       <c r="H138" t="s">
-        <v>9</v>
-      </c>
-      <c r="I138" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A139">
         <v>13</v>
       </c>
@@ -5920,13 +4587,10 @@
         <v>74</v>
       </c>
       <c r="H139" t="s">
-        <v>9</v>
-      </c>
-      <c r="I139" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A140">
         <v>14</v>
       </c>
@@ -5949,13 +4613,10 @@
         <v>74</v>
       </c>
       <c r="H140" t="s">
-        <v>9</v>
-      </c>
-      <c r="I140" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A141">
         <v>14</v>
       </c>
@@ -5978,13 +4639,10 @@
         <v>74</v>
       </c>
       <c r="H141" t="s">
-        <v>9</v>
-      </c>
-      <c r="I141" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A142">
         <v>14</v>
       </c>
@@ -6007,13 +4665,10 @@
         <v>74</v>
       </c>
       <c r="H142" t="s">
-        <v>9</v>
-      </c>
-      <c r="I142" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A143">
         <v>29</v>
       </c>
@@ -6036,13 +4691,10 @@
         <v>74</v>
       </c>
       <c r="H143" t="s">
-        <v>30</v>
-      </c>
-      <c r="I143" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A144">
         <v>26</v>
       </c>
@@ -6065,13 +4717,10 @@
         <v>74</v>
       </c>
       <c r="H144" t="s">
-        <v>30</v>
-      </c>
-      <c r="I144" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A145">
         <v>26</v>
       </c>
@@ -6094,13 +4743,10 @@
         <v>74</v>
       </c>
       <c r="H145" t="s">
-        <v>30</v>
-      </c>
-      <c r="I145" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A146">
         <v>31</v>
       </c>
@@ -6123,13 +4769,10 @@
         <v>74</v>
       </c>
       <c r="H146" t="s">
-        <v>24</v>
-      </c>
-      <c r="I146" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A147">
         <v>32</v>
       </c>
@@ -6152,13 +4795,10 @@
         <v>74</v>
       </c>
       <c r="H147" t="s">
-        <v>24</v>
-      </c>
-      <c r="I147" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A148">
         <v>28</v>
       </c>
@@ -6181,13 +4821,10 @@
         <v>74</v>
       </c>
       <c r="H148" t="s">
-        <v>9</v>
-      </c>
-      <c r="I148" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A149">
         <v>24</v>
       </c>
@@ -6210,13 +4847,10 @@
         <v>74</v>
       </c>
       <c r="H149" t="s">
-        <v>30</v>
-      </c>
-      <c r="I149" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A150">
         <v>26</v>
       </c>
@@ -6239,13 +4873,10 @@
         <v>74</v>
       </c>
       <c r="H150" t="s">
-        <v>30</v>
-      </c>
-      <c r="I150" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A151">
         <v>24</v>
       </c>
@@ -6268,13 +4899,10 @@
         <v>74</v>
       </c>
       <c r="H151" t="s">
-        <v>24</v>
-      </c>
-      <c r="I151" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A152">
         <v>26</v>
       </c>
@@ -6297,13 +4925,10 @@
         <v>74</v>
       </c>
       <c r="H152" t="s">
-        <v>24</v>
-      </c>
-      <c r="I152" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A153">
         <v>31</v>
       </c>
@@ -6326,13 +4951,10 @@
         <v>74</v>
       </c>
       <c r="H153" t="s">
-        <v>30</v>
-      </c>
-      <c r="I153" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A154">
         <v>19</v>
       </c>
@@ -6355,13 +4977,10 @@
         <v>75</v>
       </c>
       <c r="H154" t="s">
-        <v>9</v>
-      </c>
-      <c r="I154" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A155">
         <v>18</v>
       </c>
@@ -6384,13 +5003,10 @@
         <v>75</v>
       </c>
       <c r="H155" t="s">
-        <v>9</v>
-      </c>
-      <c r="I155" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A156">
         <v>15</v>
       </c>
@@ -6413,13 +5029,10 @@
         <v>75</v>
       </c>
       <c r="H156" t="s">
-        <v>9</v>
-      </c>
-      <c r="I156" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A157">
         <v>15</v>
       </c>
@@ -6442,13 +5055,10 @@
         <v>75</v>
       </c>
       <c r="H157" t="s">
-        <v>9</v>
-      </c>
-      <c r="I157" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A158">
         <v>16</v>
       </c>
@@ -6471,13 +5081,10 @@
         <v>75</v>
       </c>
       <c r="H158" t="s">
-        <v>9</v>
-      </c>
-      <c r="I158" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A159">
         <v>15</v>
       </c>
@@ -6500,13 +5107,10 @@
         <v>75</v>
       </c>
       <c r="H159" t="s">
-        <v>9</v>
-      </c>
-      <c r="I159" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A160">
         <v>16</v>
       </c>
@@ -6529,13 +5133,10 @@
         <v>75</v>
       </c>
       <c r="H160" t="s">
-        <v>9</v>
-      </c>
-      <c r="I160" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A161">
         <v>14</v>
       </c>
@@ -6558,13 +5159,10 @@
         <v>75</v>
       </c>
       <c r="H161" t="s">
-        <v>9</v>
-      </c>
-      <c r="I161" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A162">
         <v>17</v>
       </c>
@@ -6587,13 +5185,10 @@
         <v>75</v>
       </c>
       <c r="H162" t="s">
-        <v>9</v>
-      </c>
-      <c r="I162" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A163">
         <v>16</v>
       </c>
@@ -6616,13 +5211,10 @@
         <v>75</v>
       </c>
       <c r="H163" t="s">
-        <v>9</v>
-      </c>
-      <c r="I163" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A164">
         <v>15</v>
       </c>
@@ -6645,13 +5237,10 @@
         <v>75</v>
       </c>
       <c r="H164" t="s">
-        <v>9</v>
-      </c>
-      <c r="I164" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A165">
         <v>18</v>
       </c>
@@ -6674,13 +5263,10 @@
         <v>75</v>
       </c>
       <c r="H165" t="s">
-        <v>9</v>
-      </c>
-      <c r="I165" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A166">
         <v>21</v>
       </c>
@@ -6703,13 +5289,10 @@
         <v>75</v>
       </c>
       <c r="H166" t="s">
-        <v>9</v>
-      </c>
-      <c r="I166" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A167">
         <v>20</v>
       </c>
@@ -6732,13 +5315,10 @@
         <v>75</v>
       </c>
       <c r="H167" t="s">
-        <v>9</v>
-      </c>
-      <c r="I167" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A168">
         <v>13</v>
       </c>
@@ -6761,13 +5341,10 @@
         <v>75</v>
       </c>
       <c r="H168" t="s">
-        <v>9</v>
-      </c>
-      <c r="I168" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A169">
         <v>29</v>
       </c>
@@ -6790,13 +5367,10 @@
         <v>75</v>
       </c>
       <c r="H169" t="s">
-        <v>24</v>
-      </c>
-      <c r="I169" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A170">
         <v>23</v>
       </c>
@@ -6819,13 +5393,10 @@
         <v>75</v>
       </c>
       <c r="H170" t="s">
-        <v>9</v>
-      </c>
-      <c r="I170" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A171">
         <v>20</v>
       </c>
@@ -6848,13 +5419,10 @@
         <v>75</v>
       </c>
       <c r="H171" t="s">
-        <v>9</v>
-      </c>
-      <c r="I171" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A172">
         <v>23</v>
       </c>
@@ -6877,13 +5445,10 @@
         <v>75</v>
       </c>
       <c r="H172" t="s">
-        <v>9</v>
-      </c>
-      <c r="I172" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A173">
         <v>24</v>
       </c>
@@ -6906,13 +5471,10 @@
         <v>75</v>
       </c>
       <c r="H173" t="s">
-        <v>24</v>
-      </c>
-      <c r="I173" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A174">
         <v>25</v>
       </c>
@@ -6935,13 +5497,10 @@
         <v>75</v>
       </c>
       <c r="H174" t="s">
-        <v>30</v>
-      </c>
-      <c r="I174" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A175">
         <v>24</v>
       </c>
@@ -6964,13 +5523,10 @@
         <v>75</v>
       </c>
       <c r="H175" t="s">
-        <v>24</v>
-      </c>
-      <c r="I175" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A176">
         <v>18</v>
       </c>
@@ -6993,13 +5549,10 @@
         <v>75</v>
       </c>
       <c r="H176" t="s">
-        <v>9</v>
-      </c>
-      <c r="I176" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A177">
         <v>29</v>
       </c>
@@ -7022,13 +5575,10 @@
         <v>75</v>
       </c>
       <c r="H177" t="s">
-        <v>30</v>
-      </c>
-      <c r="I177" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A178">
         <v>19</v>
       </c>
@@ -7051,13 +5601,10 @@
         <v>75</v>
       </c>
       <c r="H178" t="s">
-        <v>9</v>
-      </c>
-      <c r="I178" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A179">
         <v>23</v>
       </c>
@@ -7080,13 +5627,10 @@
         <v>75</v>
       </c>
       <c r="H179" t="s">
-        <v>30</v>
-      </c>
-      <c r="I179" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A180">
         <v>23</v>
       </c>
@@ -7109,13 +5653,10 @@
         <v>75</v>
       </c>
       <c r="H180" t="s">
-        <v>30</v>
-      </c>
-      <c r="I180" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A181">
         <v>22</v>
       </c>
@@ -7138,13 +5679,10 @@
         <v>75</v>
       </c>
       <c r="H181" t="s">
-        <v>30</v>
-      </c>
-      <c r="I181" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A182">
         <v>25</v>
       </c>
@@ -7167,13 +5705,10 @@
         <v>75</v>
       </c>
       <c r="H182" t="s">
-        <v>30</v>
-      </c>
-      <c r="I182" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A183">
         <v>33</v>
       </c>
@@ -7196,13 +5731,10 @@
         <v>75</v>
       </c>
       <c r="H183" t="s">
-        <v>24</v>
-      </c>
-      <c r="I183" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A184">
         <v>28</v>
       </c>
@@ -7225,13 +5757,10 @@
         <v>76</v>
       </c>
       <c r="H184" t="s">
-        <v>30</v>
-      </c>
-      <c r="I184" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A185">
         <v>25</v>
       </c>
@@ -7254,13 +5783,10 @@
         <v>76</v>
       </c>
       <c r="H185" t="s">
-        <v>30</v>
-      </c>
-      <c r="I185" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A186">
         <v>25</v>
       </c>
@@ -7283,13 +5809,10 @@
         <v>76</v>
       </c>
       <c r="H186" t="s">
-        <v>9</v>
-      </c>
-      <c r="I186" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A187">
         <v>26</v>
       </c>
@@ -7312,13 +5835,10 @@
         <v>76</v>
       </c>
       <c r="H187" t="s">
-        <v>9</v>
-      </c>
-      <c r="I187" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A188">
         <v>27</v>
       </c>
@@ -7341,13 +5861,10 @@
         <v>76</v>
       </c>
       <c r="H188" t="s">
-        <v>30</v>
-      </c>
-      <c r="I188" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A189">
         <v>17.5</v>
       </c>
@@ -7370,13 +5887,10 @@
         <v>76</v>
       </c>
       <c r="H189" t="s">
-        <v>9</v>
-      </c>
-      <c r="I189" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A190">
         <v>16</v>
       </c>
@@ -7399,13 +5913,10 @@
         <v>76</v>
       </c>
       <c r="H190" t="s">
-        <v>9</v>
-      </c>
-      <c r="I190" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A191">
         <v>15.5</v>
       </c>
@@ -7428,13 +5939,10 @@
         <v>76</v>
       </c>
       <c r="H191" t="s">
-        <v>9</v>
-      </c>
-      <c r="I191" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A192">
         <v>14.5</v>
       </c>
@@ -7457,13 +5965,10 @@
         <v>76</v>
       </c>
       <c r="H192" t="s">
-        <v>9</v>
-      </c>
-      <c r="I192" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A193">
         <v>22</v>
       </c>
@@ -7486,13 +5991,10 @@
         <v>76</v>
       </c>
       <c r="H193" t="s">
-        <v>9</v>
-      </c>
-      <c r="I193" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A194">
         <v>22</v>
       </c>
@@ -7515,13 +6017,10 @@
         <v>76</v>
       </c>
       <c r="H194" t="s">
-        <v>9</v>
-      </c>
-      <c r="I194" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A195">
         <v>24</v>
       </c>
@@ -7544,13 +6043,10 @@
         <v>76</v>
       </c>
       <c r="H195" t="s">
-        <v>9</v>
-      </c>
-      <c r="I195" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A196">
         <v>22.5</v>
       </c>
@@ -7573,13 +6069,10 @@
         <v>76</v>
       </c>
       <c r="H196" t="s">
-        <v>9</v>
-      </c>
-      <c r="I196" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A197">
         <v>29</v>
       </c>
@@ -7602,13 +6095,10 @@
         <v>76</v>
       </c>
       <c r="H197" t="s">
-        <v>9</v>
-      </c>
-      <c r="I197" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A198">
         <v>24.5</v>
       </c>
@@ -7631,13 +6121,10 @@
         <v>76</v>
       </c>
       <c r="H198" t="s">
-        <v>9</v>
-      </c>
-      <c r="I198" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A199">
         <v>29</v>
       </c>
@@ -7660,13 +6147,10 @@
         <v>76</v>
       </c>
       <c r="H199" t="s">
-        <v>30</v>
-      </c>
-      <c r="I199" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A200">
         <v>33</v>
       </c>
@@ -7689,13 +6173,10 @@
         <v>76</v>
       </c>
       <c r="H200" t="s">
-        <v>24</v>
-      </c>
-      <c r="I200" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A201">
         <v>20</v>
       </c>
@@ -7718,13 +6199,10 @@
         <v>76</v>
       </c>
       <c r="H201" t="s">
-        <v>9</v>
-      </c>
-      <c r="I201" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A202">
         <v>18</v>
       </c>
@@ -7747,13 +6225,10 @@
         <v>76</v>
       </c>
       <c r="H202" t="s">
-        <v>9</v>
-      </c>
-      <c r="I202" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A203">
         <v>18.5</v>
       </c>
@@ -7776,13 +6251,10 @@
         <v>76</v>
       </c>
       <c r="H203" t="s">
-        <v>9</v>
-      </c>
-      <c r="I203" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A204">
         <v>17.5</v>
       </c>
@@ -7805,13 +6277,10 @@
         <v>76</v>
       </c>
       <c r="H204" t="s">
-        <v>9</v>
-      </c>
-      <c r="I204" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A205">
         <v>29.5</v>
       </c>
@@ -7834,13 +6303,10 @@
         <v>76</v>
       </c>
       <c r="H205" t="s">
-        <v>30</v>
-      </c>
-      <c r="I205" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A206">
         <v>32</v>
       </c>
@@ -7863,13 +6329,10 @@
         <v>76</v>
       </c>
       <c r="H206" t="s">
-        <v>24</v>
-      </c>
-      <c r="I206" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A207">
         <v>28</v>
       </c>
@@ -7892,13 +6355,10 @@
         <v>76</v>
       </c>
       <c r="H207" t="s">
-        <v>24</v>
-      </c>
-      <c r="I207" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A208">
         <v>26.5</v>
       </c>
@@ -7921,13 +6381,10 @@
         <v>76</v>
       </c>
       <c r="H208" t="s">
-        <v>9</v>
-      </c>
-      <c r="I208" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A209">
         <v>20</v>
       </c>
@@ -7950,13 +6407,10 @@
         <v>76</v>
       </c>
       <c r="H209" t="s">
-        <v>30</v>
-      </c>
-      <c r="I209" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A210">
         <v>13</v>
       </c>
@@ -7979,13 +6433,10 @@
         <v>76</v>
       </c>
       <c r="H210" t="s">
-        <v>9</v>
-      </c>
-      <c r="I210" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A211">
         <v>19</v>
       </c>
@@ -8008,13 +6459,10 @@
         <v>76</v>
       </c>
       <c r="H211" t="s">
-        <v>30</v>
-      </c>
-      <c r="I211" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A212">
         <v>19</v>
       </c>
@@ -8037,13 +6485,10 @@
         <v>76</v>
       </c>
       <c r="H212" t="s">
-        <v>24</v>
-      </c>
-      <c r="I212" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A213">
         <v>16.5</v>
       </c>
@@ -8066,13 +6511,10 @@
         <v>76</v>
       </c>
       <c r="H213" t="s">
-        <v>30</v>
-      </c>
-      <c r="I213" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A214">
         <v>16.5</v>
       </c>
@@ -8095,13 +6537,10 @@
         <v>76</v>
       </c>
       <c r="H214" t="s">
-        <v>9</v>
-      </c>
-      <c r="I214" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A215">
         <v>13</v>
       </c>
@@ -8124,13 +6563,10 @@
         <v>76</v>
       </c>
       <c r="H215" t="s">
-        <v>9</v>
-      </c>
-      <c r="I215" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A216">
         <v>13</v>
       </c>
@@ -8153,13 +6589,10 @@
         <v>76</v>
       </c>
       <c r="H216" t="s">
-        <v>9</v>
-      </c>
-      <c r="I216" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A217">
         <v>13</v>
       </c>
@@ -8182,13 +6615,10 @@
         <v>76</v>
       </c>
       <c r="H217" t="s">
-        <v>9</v>
-      </c>
-      <c r="I217" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A218">
         <v>31.5</v>
       </c>
@@ -8211,13 +6641,10 @@
         <v>77</v>
       </c>
       <c r="H218" t="s">
-        <v>24</v>
-      </c>
-      <c r="I218" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A219">
         <v>30</v>
       </c>
@@ -8240,13 +6667,10 @@
         <v>77</v>
       </c>
       <c r="H219" t="s">
-        <v>9</v>
-      </c>
-      <c r="I219" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A220">
         <v>36</v>
       </c>
@@ -8269,13 +6693,10 @@
         <v>77</v>
       </c>
       <c r="H220" t="s">
-        <v>30</v>
-      </c>
-      <c r="I220" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A221">
         <v>25.5</v>
       </c>
@@ -8298,13 +6719,10 @@
         <v>77</v>
       </c>
       <c r="H221" t="s">
-        <v>9</v>
-      </c>
-      <c r="I221" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A222">
         <v>33.5</v>
       </c>
@@ -8327,13 +6745,10 @@
         <v>77</v>
       </c>
       <c r="H222" t="s">
-        <v>24</v>
-      </c>
-      <c r="I222" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A223">
         <v>17.5</v>
       </c>
@@ -8356,13 +6771,10 @@
         <v>77</v>
       </c>
       <c r="H223" t="s">
-        <v>9</v>
-      </c>
-      <c r="I223" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A224">
         <v>17</v>
       </c>
@@ -8385,13 +6797,10 @@
         <v>77</v>
       </c>
       <c r="H224" t="s">
-        <v>9</v>
-      </c>
-      <c r="I224" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A225">
         <v>15.5</v>
       </c>
@@ -8414,13 +6823,10 @@
         <v>77</v>
       </c>
       <c r="H225" t="s">
-        <v>9</v>
-      </c>
-      <c r="I225" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A226">
         <v>15</v>
       </c>
@@ -8443,13 +6849,10 @@
         <v>77</v>
       </c>
       <c r="H226" t="s">
-        <v>9</v>
-      </c>
-      <c r="I226" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A227">
         <v>17.5</v>
       </c>
@@ -8472,13 +6875,10 @@
         <v>77</v>
       </c>
       <c r="H227" t="s">
-        <v>9</v>
-      </c>
-      <c r="I227" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A228">
         <v>20.5</v>
       </c>
@@ -8501,13 +6901,10 @@
         <v>77</v>
       </c>
       <c r="H228" t="s">
-        <v>9</v>
-      </c>
-      <c r="I228" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A229">
         <v>19</v>
       </c>
@@ -8530,13 +6927,10 @@
         <v>77</v>
       </c>
       <c r="H229" t="s">
-        <v>9</v>
-      </c>
-      <c r="I229" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A230">
         <v>18.5</v>
       </c>
@@ -8559,13 +6953,10 @@
         <v>77</v>
       </c>
       <c r="H230" t="s">
-        <v>9</v>
-      </c>
-      <c r="I230" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A231">
         <v>16</v>
       </c>
@@ -8588,13 +6979,10 @@
         <v>77</v>
       </c>
       <c r="H231" t="s">
-        <v>9</v>
-      </c>
-      <c r="I231" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A232">
         <v>15.5</v>
       </c>
@@ -8617,13 +7005,10 @@
         <v>77</v>
       </c>
       <c r="H232" t="s">
-        <v>9</v>
-      </c>
-      <c r="I232" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A233">
         <v>15.5</v>
       </c>
@@ -8646,13 +7031,10 @@
         <v>77</v>
       </c>
       <c r="H233" t="s">
-        <v>9</v>
-      </c>
-      <c r="I233" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A234">
         <v>16</v>
       </c>
@@ -8675,13 +7057,10 @@
         <v>77</v>
       </c>
       <c r="H234" t="s">
-        <v>9</v>
-      </c>
-      <c r="I234" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A235">
         <v>29</v>
       </c>
@@ -8704,13 +7083,10 @@
         <v>77</v>
       </c>
       <c r="H235" t="s">
-        <v>30</v>
-      </c>
-      <c r="I235" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A236">
         <v>24.5</v>
       </c>
@@ -8733,13 +7109,10 @@
         <v>77</v>
       </c>
       <c r="H236" t="s">
-        <v>9</v>
-      </c>
-      <c r="I236" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A237">
         <v>26</v>
       </c>
@@ -8762,13 +7135,10 @@
         <v>77</v>
       </c>
       <c r="H237" t="s">
-        <v>24</v>
-      </c>
-      <c r="I237" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A238">
         <v>25.5</v>
       </c>
@@ -8791,13 +7161,10 @@
         <v>77</v>
       </c>
       <c r="H238" t="s">
-        <v>9</v>
-      </c>
-      <c r="I238" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A239">
         <v>30.5</v>
       </c>
@@ -8820,13 +7187,10 @@
         <v>77</v>
       </c>
       <c r="H239" t="s">
-        <v>9</v>
-      </c>
-      <c r="I239" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A240">
         <v>33.5</v>
       </c>
@@ -8849,13 +7213,10 @@
         <v>77</v>
       </c>
       <c r="H240" t="s">
-        <v>9</v>
-      </c>
-      <c r="I240" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A241">
         <v>30</v>
       </c>
@@ -8878,13 +7239,10 @@
         <v>77</v>
       </c>
       <c r="H241" t="s">
-        <v>24</v>
-      </c>
-      <c r="I241" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A242">
         <v>30.5</v>
       </c>
@@ -8907,13 +7265,10 @@
         <v>77</v>
       </c>
       <c r="H242" t="s">
-        <v>30</v>
-      </c>
-      <c r="I242" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A243">
         <v>22</v>
       </c>
@@ -8936,13 +7291,10 @@
         <v>77</v>
       </c>
       <c r="H243" t="s">
-        <v>24</v>
-      </c>
-      <c r="I243" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A244">
         <v>21.5</v>
       </c>
@@ -8965,13 +7317,10 @@
         <v>77</v>
       </c>
       <c r="H244" t="s">
-        <v>30</v>
-      </c>
-      <c r="I244" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A245">
         <v>21.5</v>
       </c>
@@ -8994,13 +7343,10 @@
         <v>77</v>
       </c>
       <c r="H245" t="s">
-        <v>24</v>
-      </c>
-      <c r="I245" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A246">
         <v>43.1</v>
       </c>
@@ -9023,13 +7369,10 @@
         <v>78</v>
       </c>
       <c r="H246" t="s">
-        <v>30</v>
-      </c>
-      <c r="I246" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A247">
         <v>36.1</v>
       </c>
@@ -9052,13 +7395,10 @@
         <v>78</v>
       </c>
       <c r="H247" t="s">
-        <v>9</v>
-      </c>
-      <c r="I247" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A248">
         <v>32.799999999999997</v>
       </c>
@@ -9081,13 +7421,10 @@
         <v>78</v>
       </c>
       <c r="H248" t="s">
-        <v>24</v>
-      </c>
-      <c r="I248" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A249">
         <v>39.4</v>
       </c>
@@ -9110,13 +7447,10 @@
         <v>78</v>
       </c>
       <c r="H249" t="s">
-        <v>24</v>
-      </c>
-      <c r="I249" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A250">
         <v>36.1</v>
       </c>
@@ -9139,13 +7473,10 @@
         <v>78</v>
       </c>
       <c r="H250" t="s">
-        <v>24</v>
-      </c>
-      <c r="I250" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A251">
         <v>19.899999999999999</v>
       </c>
@@ -9168,13 +7499,10 @@
         <v>78</v>
       </c>
       <c r="H251" t="s">
-        <v>9</v>
-      </c>
-      <c r="I251" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A252">
         <v>19.399999999999999</v>
       </c>
@@ -9197,13 +7525,10 @@
         <v>78</v>
       </c>
       <c r="H252" t="s">
-        <v>9</v>
-      </c>
-      <c r="I252" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A253">
         <v>20.2</v>
       </c>
@@ -9226,13 +7551,10 @@
         <v>78</v>
       </c>
       <c r="H253" t="s">
-        <v>9</v>
-      </c>
-      <c r="I253" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A254">
         <v>19.2</v>
       </c>
@@ -9255,13 +7577,10 @@
         <v>78</v>
       </c>
       <c r="H254" t="s">
-        <v>9</v>
-      </c>
-      <c r="I254" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A255">
         <v>20.5</v>
       </c>
@@ -9284,13 +7603,10 @@
         <v>78</v>
       </c>
       <c r="H255" t="s">
-        <v>9</v>
-      </c>
-      <c r="I255" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A256">
         <v>20.2</v>
       </c>
@@ -9313,13 +7629,10 @@
         <v>78</v>
       </c>
       <c r="H256" t="s">
-        <v>9</v>
-      </c>
-      <c r="I256" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A257">
         <v>25.1</v>
       </c>
@@ -9342,13 +7655,10 @@
         <v>78</v>
       </c>
       <c r="H257" t="s">
-        <v>9</v>
-      </c>
-      <c r="I257" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A258">
         <v>20.5</v>
       </c>
@@ -9371,13 +7681,10 @@
         <v>78</v>
       </c>
       <c r="H258" t="s">
-        <v>9</v>
-      </c>
-      <c r="I258" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A259">
         <v>19.399999999999999</v>
       </c>
@@ -9400,13 +7707,10 @@
         <v>78</v>
       </c>
       <c r="H259" t="s">
-        <v>9</v>
-      </c>
-      <c r="I259" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A260">
         <v>20.6</v>
       </c>
@@ -9429,13 +7733,10 @@
         <v>78</v>
       </c>
       <c r="H260" t="s">
-        <v>9</v>
-      </c>
-      <c r="I260" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A261">
         <v>20.8</v>
       </c>
@@ -9458,13 +7759,10 @@
         <v>78</v>
       </c>
       <c r="H261" t="s">
-        <v>9</v>
-      </c>
-      <c r="I261" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A262">
         <v>18.600000000000001</v>
       </c>
@@ -9487,13 +7785,10 @@
         <v>78</v>
       </c>
       <c r="H262" t="s">
-        <v>9</v>
-      </c>
-      <c r="I262" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A263">
         <v>18.100000000000001</v>
       </c>
@@ -9516,13 +7811,10 @@
         <v>78</v>
       </c>
       <c r="H263" t="s">
-        <v>9</v>
-      </c>
-      <c r="I263" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A264">
         <v>19.2</v>
       </c>
@@ -9545,13 +7837,10 @@
         <v>78</v>
       </c>
       <c r="H264" t="s">
-        <v>9</v>
-      </c>
-      <c r="I264" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A265">
         <v>17.7</v>
       </c>
@@ -9574,13 +7863,10 @@
         <v>78</v>
       </c>
       <c r="H265" t="s">
-        <v>9</v>
-      </c>
-      <c r="I265" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A266">
         <v>18.100000000000001</v>
       </c>
@@ -9603,13 +7889,10 @@
         <v>78</v>
       </c>
       <c r="H266" t="s">
-        <v>9</v>
-      </c>
-      <c r="I266" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A267">
         <v>17.5</v>
       </c>
@@ -9632,13 +7915,10 @@
         <v>78</v>
       </c>
       <c r="H267" t="s">
-        <v>9</v>
-      </c>
-      <c r="I267" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A268">
         <v>30</v>
       </c>
@@ -9661,13 +7941,10 @@
         <v>78</v>
       </c>
       <c r="H268" t="s">
-        <v>9</v>
-      </c>
-      <c r="I268" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A269">
         <v>27.5</v>
       </c>
@@ -9690,13 +7967,10 @@
         <v>78</v>
       </c>
       <c r="H269" t="s">
-        <v>24</v>
-      </c>
-      <c r="I269" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A270">
         <v>27.2</v>
       </c>
@@ -9719,13 +7993,10 @@
         <v>78</v>
       </c>
       <c r="H270" t="s">
-        <v>24</v>
-      </c>
-      <c r="I270" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A271">
         <v>30.9</v>
       </c>
@@ -9748,13 +8019,10 @@
         <v>78</v>
       </c>
       <c r="H271" t="s">
-        <v>9</v>
-      </c>
-      <c r="I271" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A272">
         <v>21.1</v>
       </c>
@@ -9777,13 +8045,10 @@
         <v>78</v>
       </c>
       <c r="H272" t="s">
-        <v>24</v>
-      </c>
-      <c r="I272" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A273">
         <v>23.2</v>
       </c>
@@ -9806,13 +8071,10 @@
         <v>78</v>
       </c>
       <c r="H273" t="s">
-        <v>9</v>
-      </c>
-      <c r="I273" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A274">
         <v>23.8</v>
       </c>
@@ -9835,13 +8097,10 @@
         <v>78</v>
       </c>
       <c r="H274" t="s">
-        <v>9</v>
-      </c>
-      <c r="I274" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A275">
         <v>23.9</v>
       </c>
@@ -9864,13 +8123,10 @@
         <v>78</v>
       </c>
       <c r="H275" t="s">
-        <v>24</v>
-      </c>
-      <c r="I275" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A276">
         <v>20.3</v>
       </c>
@@ -9893,13 +8149,10 @@
         <v>78</v>
       </c>
       <c r="H276" t="s">
-        <v>30</v>
-      </c>
-      <c r="I276" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A277">
         <v>17</v>
       </c>
@@ -9922,13 +8175,10 @@
         <v>78</v>
       </c>
       <c r="H277" t="s">
-        <v>30</v>
-      </c>
-      <c r="I277" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A278">
         <v>21.6</v>
       </c>
@@ -9951,13 +8201,10 @@
         <v>78</v>
       </c>
       <c r="H278" t="s">
-        <v>30</v>
-      </c>
-      <c r="I278" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A279">
         <v>16.2</v>
       </c>
@@ -9980,13 +8227,10 @@
         <v>78</v>
       </c>
       <c r="H279" t="s">
-        <v>30</v>
-      </c>
-      <c r="I279" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A280">
         <v>31.5</v>
       </c>
@@ -10009,13 +8253,10 @@
         <v>78</v>
       </c>
       <c r="H280" t="s">
-        <v>30</v>
-      </c>
-      <c r="I280" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A281">
         <v>29.5</v>
       </c>
@@ -10038,13 +8279,10 @@
         <v>78</v>
       </c>
       <c r="H281" t="s">
-        <v>24</v>
-      </c>
-      <c r="I281" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A282">
         <v>21.5</v>
       </c>
@@ -10067,13 +8305,10 @@
         <v>79</v>
       </c>
       <c r="H282" t="s">
-        <v>9</v>
-      </c>
-      <c r="I282" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A283">
         <v>19.8</v>
       </c>
@@ -10096,13 +8331,10 @@
         <v>79</v>
       </c>
       <c r="H283" t="s">
-        <v>9</v>
-      </c>
-      <c r="I283" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A284">
         <v>22.3</v>
       </c>
@@ -10125,13 +8357,10 @@
         <v>79</v>
       </c>
       <c r="H284" t="s">
-        <v>9</v>
-      </c>
-      <c r="I284" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A285">
         <v>20.2</v>
       </c>
@@ -10154,13 +8383,10 @@
         <v>79</v>
       </c>
       <c r="H285" t="s">
-        <v>9</v>
-      </c>
-      <c r="I285" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A286">
         <v>20.6</v>
       </c>
@@ -10183,13 +8409,10 @@
         <v>79</v>
       </c>
       <c r="H286" t="s">
-        <v>9</v>
-      </c>
-      <c r="I286" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10212,13 +8435,10 @@
         <v>79</v>
       </c>
       <c r="H287" t="s">
-        <v>9</v>
-      </c>
-      <c r="I287" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A288">
         <v>17.600000000000001</v>
       </c>
@@ -10241,13 +8461,10 @@
         <v>79</v>
       </c>
       <c r="H288" t="s">
-        <v>9</v>
-      </c>
-      <c r="I288" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A289">
         <v>16.5</v>
       </c>
@@ -10270,13 +8487,10 @@
         <v>79</v>
       </c>
       <c r="H289" t="s">
-        <v>9</v>
-      </c>
-      <c r="I289" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A290">
         <v>18.2</v>
       </c>
@@ -10299,13 +8513,10 @@
         <v>79</v>
       </c>
       <c r="H290" t="s">
-        <v>9</v>
-      </c>
-      <c r="I290" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A291">
         <v>16.899999999999999</v>
       </c>
@@ -10328,13 +8539,10 @@
         <v>79</v>
       </c>
       <c r="H291" t="s">
-        <v>9</v>
-      </c>
-      <c r="I291" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A292">
         <v>15.5</v>
       </c>
@@ -10357,13 +8565,10 @@
         <v>79</v>
       </c>
       <c r="H292" t="s">
-        <v>9</v>
-      </c>
-      <c r="I292" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A293">
         <v>19.2</v>
       </c>
@@ -10386,13 +8591,10 @@
         <v>79</v>
       </c>
       <c r="H293" t="s">
-        <v>9</v>
-      </c>
-      <c r="I293" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A294">
         <v>18.5</v>
       </c>
@@ -10415,13 +8617,10 @@
         <v>79</v>
       </c>
       <c r="H294" t="s">
-        <v>9</v>
-      </c>
-      <c r="I294" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A295">
         <v>31.9</v>
       </c>
@@ -10444,13 +8643,10 @@
         <v>79</v>
       </c>
       <c r="H295" t="s">
-        <v>30</v>
-      </c>
-      <c r="I295" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A296">
         <v>34.1</v>
       </c>
@@ -10473,13 +8669,10 @@
         <v>79</v>
       </c>
       <c r="H296" t="s">
-        <v>24</v>
-      </c>
-      <c r="I296" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A297">
         <v>35.700000000000003</v>
       </c>
@@ -10502,13 +8695,10 @@
         <v>79</v>
       </c>
       <c r="H297" t="s">
-        <v>9</v>
-      </c>
-      <c r="I297" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A298">
         <v>27.4</v>
       </c>
@@ -10531,13 +8721,10 @@
         <v>79</v>
       </c>
       <c r="H298" t="s">
-        <v>9</v>
-      </c>
-      <c r="I298" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A299">
         <v>25.4</v>
       </c>
@@ -10560,13 +8747,10 @@
         <v>79</v>
       </c>
       <c r="H299" t="s">
-        <v>30</v>
-      </c>
-      <c r="I299" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A300">
         <v>23</v>
       </c>
@@ -10589,13 +8773,10 @@
         <v>79</v>
       </c>
       <c r="H300" t="s">
-        <v>9</v>
-      </c>
-      <c r="I300" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A301">
         <v>27.2</v>
       </c>
@@ -10618,13 +8799,10 @@
         <v>79</v>
       </c>
       <c r="H301" t="s">
-        <v>30</v>
-      </c>
-      <c r="I301" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A302">
         <v>23.9</v>
       </c>
@@ -10647,13 +8825,10 @@
         <v>79</v>
       </c>
       <c r="H302" t="s">
-        <v>9</v>
-      </c>
-      <c r="I302" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A303">
         <v>34.200000000000003</v>
       </c>
@@ -10676,13 +8851,10 @@
         <v>79</v>
       </c>
       <c r="H303" t="s">
-        <v>9</v>
-      </c>
-      <c r="I303" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A304">
         <v>34.5</v>
       </c>
@@ -10705,13 +8877,10 @@
         <v>79</v>
       </c>
       <c r="H304" t="s">
-        <v>9</v>
-      </c>
-      <c r="I304" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A305">
         <v>31.8</v>
       </c>
@@ -10734,13 +8903,10 @@
         <v>79</v>
       </c>
       <c r="H305" t="s">
-        <v>24</v>
-      </c>
-      <c r="I305" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A306">
         <v>37.299999999999997</v>
       </c>
@@ -10763,13 +8929,10 @@
         <v>79</v>
       </c>
       <c r="H306" t="s">
-        <v>30</v>
-      </c>
-      <c r="I306" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A307">
         <v>28.4</v>
       </c>
@@ -10792,13 +8955,10 @@
         <v>79</v>
       </c>
       <c r="H307" t="s">
-        <v>9</v>
-      </c>
-      <c r="I307" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A308">
         <v>28.8</v>
       </c>
@@ -10821,13 +8981,10 @@
         <v>79</v>
       </c>
       <c r="H308" t="s">
-        <v>9</v>
-      </c>
-      <c r="I308" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A309">
         <v>26.8</v>
       </c>
@@ -10850,13 +9007,10 @@
         <v>79</v>
       </c>
       <c r="H309" t="s">
-        <v>9</v>
-      </c>
-      <c r="I309" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A310">
         <v>33.5</v>
       </c>
@@ -10879,13 +9033,10 @@
         <v>79</v>
       </c>
       <c r="H310" t="s">
-        <v>9</v>
-      </c>
-      <c r="I310" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A311">
         <v>41.5</v>
       </c>
@@ -10908,13 +9059,10 @@
         <v>80</v>
       </c>
       <c r="H311" t="s">
-        <v>30</v>
-      </c>
-      <c r="I311" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A312">
         <v>38.1</v>
       </c>
@@ -10937,13 +9085,10 @@
         <v>80</v>
       </c>
       <c r="H312" t="s">
-        <v>24</v>
-      </c>
-      <c r="I312" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A313">
         <v>32.1</v>
       </c>
@@ -10966,13 +9111,10 @@
         <v>80</v>
       </c>
       <c r="H313" t="s">
-        <v>9</v>
-      </c>
-      <c r="I313" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A314">
         <v>37.200000000000003</v>
       </c>
@@ -10995,13 +9137,10 @@
         <v>80</v>
       </c>
       <c r="H314" t="s">
-        <v>24</v>
-      </c>
-      <c r="I314" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A315">
         <v>28</v>
       </c>
@@ -11024,13 +9163,10 @@
         <v>80</v>
       </c>
       <c r="H315" t="s">
-        <v>9</v>
-      </c>
-      <c r="I315" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A316">
         <v>26.4</v>
       </c>
@@ -11053,13 +9189,10 @@
         <v>80</v>
       </c>
       <c r="H316" t="s">
-        <v>9</v>
-      </c>
-      <c r="I316" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A317">
         <v>24.3</v>
       </c>
@@ -11082,13 +9215,10 @@
         <v>80</v>
       </c>
       <c r="H317" t="s">
-        <v>9</v>
-      </c>
-      <c r="I317" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A318">
         <v>19.100000000000001</v>
       </c>
@@ -11111,13 +9241,10 @@
         <v>80</v>
       </c>
       <c r="H318" t="s">
-        <v>9</v>
-      </c>
-      <c r="I318" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A319">
         <v>34.299999999999997</v>
       </c>
@@ -11140,13 +9267,10 @@
         <v>80</v>
       </c>
       <c r="H319" t="s">
-        <v>30</v>
-      </c>
-      <c r="I319" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A320">
         <v>29.8</v>
       </c>
@@ -11169,13 +9293,10 @@
         <v>80</v>
       </c>
       <c r="H320" t="s">
-        <v>24</v>
-      </c>
-      <c r="I320" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A321">
         <v>31.3</v>
       </c>
@@ -11198,13 +9319,10 @@
         <v>80</v>
       </c>
       <c r="H321" t="s">
-        <v>24</v>
-      </c>
-      <c r="I321" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A322">
         <v>37</v>
       </c>
@@ -11227,13 +9345,10 @@
         <v>80</v>
       </c>
       <c r="H322" t="s">
-        <v>24</v>
-      </c>
-      <c r="I322" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A323">
         <v>32.200000000000003</v>
       </c>
@@ -11256,13 +9371,10 @@
         <v>80</v>
       </c>
       <c r="H323" t="s">
-        <v>24</v>
-      </c>
-      <c r="I323" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A324">
         <v>46.6</v>
       </c>
@@ -11285,13 +9397,10 @@
         <v>80</v>
       </c>
       <c r="H324" t="s">
-        <v>24</v>
-      </c>
-      <c r="I324" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A325">
         <v>27.9</v>
       </c>
@@ -11314,13 +9423,10 @@
         <v>80</v>
       </c>
       <c r="H325" t="s">
-        <v>9</v>
-      </c>
-      <c r="I325" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A326">
         <v>40.799999999999997</v>
       </c>
@@ -11343,13 +9449,10 @@
         <v>80</v>
       </c>
       <c r="H326" t="s">
-        <v>24</v>
-      </c>
-      <c r="I326" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A327">
         <v>44.3</v>
       </c>
@@ -11372,13 +9475,10 @@
         <v>80</v>
       </c>
       <c r="H327" t="s">
-        <v>30</v>
-      </c>
-      <c r="I327" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A328">
         <v>43.4</v>
       </c>
@@ -11401,13 +9501,10 @@
         <v>80</v>
       </c>
       <c r="H328" t="s">
-        <v>30</v>
-      </c>
-      <c r="I328" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A329">
         <v>36.4</v>
       </c>
@@ -11430,13 +9527,10 @@
         <v>80</v>
       </c>
       <c r="H329" t="s">
-        <v>30</v>
-      </c>
-      <c r="I329" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A330">
         <v>30</v>
       </c>
@@ -11459,13 +9553,10 @@
         <v>80</v>
       </c>
       <c r="H330" t="s">
-        <v>30</v>
-      </c>
-      <c r="I330" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A331">
         <v>44.6</v>
       </c>
@@ -11488,13 +9579,10 @@
         <v>80</v>
       </c>
       <c r="H331" t="s">
-        <v>24</v>
-      </c>
-      <c r="I331" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A332">
         <v>40.9</v>
       </c>
@@ -11514,13 +9602,10 @@
         <v>80</v>
       </c>
       <c r="H332" t="s">
-        <v>30</v>
-      </c>
-      <c r="I332" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A333">
         <v>33.799999999999997</v>
       </c>
@@ -11543,13 +9628,10 @@
         <v>80</v>
       </c>
       <c r="H333" t="s">
-        <v>24</v>
-      </c>
-      <c r="I333" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A334">
         <v>29.8</v>
       </c>
@@ -11572,13 +9654,10 @@
         <v>80</v>
       </c>
       <c r="H334" t="s">
-        <v>30</v>
-      </c>
-      <c r="I334" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A335">
         <v>32.700000000000003</v>
       </c>
@@ -11601,13 +9680,10 @@
         <v>80</v>
       </c>
       <c r="H335" t="s">
-        <v>24</v>
-      </c>
-      <c r="I335" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A336">
         <v>23.7</v>
       </c>
@@ -11630,13 +9706,10 @@
         <v>80</v>
       </c>
       <c r="H336" t="s">
-        <v>24</v>
-      </c>
-      <c r="I336" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A337">
         <v>35</v>
       </c>
@@ -11659,13 +9732,10 @@
         <v>80</v>
       </c>
       <c r="H337" t="s">
-        <v>30</v>
-      </c>
-      <c r="I337" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A338">
         <v>23.6</v>
       </c>
@@ -11685,13 +9755,10 @@
         <v>80</v>
       </c>
       <c r="H338" t="s">
-        <v>9</v>
-      </c>
-      <c r="I338" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A339">
         <v>32.4</v>
       </c>
@@ -11714,13 +9781,10 @@
         <v>80</v>
       </c>
       <c r="H339" t="s">
-        <v>24</v>
-      </c>
-      <c r="I339" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A340">
         <v>27.2</v>
       </c>
@@ -11743,13 +9807,10 @@
         <v>81</v>
       </c>
       <c r="H340" t="s">
-        <v>9</v>
-      </c>
-      <c r="I340" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A341">
         <v>26.6</v>
       </c>
@@ -11772,13 +9833,10 @@
         <v>81</v>
       </c>
       <c r="H341" t="s">
-        <v>9</v>
-      </c>
-      <c r="I341" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A342">
         <v>25.8</v>
       </c>
@@ -11801,13 +9859,10 @@
         <v>81</v>
       </c>
       <c r="H342" t="s">
-        <v>9</v>
-      </c>
-      <c r="I342" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A343">
         <v>23.5</v>
       </c>
@@ -11830,13 +9885,10 @@
         <v>81</v>
       </c>
       <c r="H343" t="s">
-        <v>9</v>
-      </c>
-      <c r="I343" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A344">
         <v>30</v>
       </c>
@@ -11859,13 +9911,10 @@
         <v>81</v>
       </c>
       <c r="H344" t="s">
-        <v>9</v>
-      </c>
-      <c r="I344" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A345">
         <v>39.1</v>
       </c>
@@ -11888,13 +9937,10 @@
         <v>81</v>
       </c>
       <c r="H345" t="s">
-        <v>24</v>
-      </c>
-      <c r="I345" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A346">
         <v>39</v>
       </c>
@@ -11917,13 +9963,10 @@
         <v>81</v>
       </c>
       <c r="H346" t="s">
-        <v>9</v>
-      </c>
-      <c r="I346" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A347">
         <v>35.1</v>
       </c>
@@ -11946,13 +9989,10 @@
         <v>81</v>
       </c>
       <c r="H347" t="s">
-        <v>24</v>
-      </c>
-      <c r="I347" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A348">
         <v>32.299999999999997</v>
       </c>
@@ -11975,13 +10015,10 @@
         <v>81</v>
       </c>
       <c r="H348" t="s">
-        <v>24</v>
-      </c>
-      <c r="I348" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A349">
         <v>37</v>
       </c>
@@ -12004,13 +10041,10 @@
         <v>81</v>
       </c>
       <c r="H349" t="s">
-        <v>24</v>
-      </c>
-      <c r="I349" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A350">
         <v>37.700000000000003</v>
       </c>
@@ -12033,13 +10067,10 @@
         <v>81</v>
       </c>
       <c r="H350" t="s">
-        <v>24</v>
-      </c>
-      <c r="I350" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A351">
         <v>34.1</v>
       </c>
@@ -12062,13 +10093,10 @@
         <v>81</v>
       </c>
       <c r="H351" t="s">
-        <v>24</v>
-      </c>
-      <c r="I351" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A352">
         <v>34.700000000000003</v>
       </c>
@@ -12091,13 +10119,10 @@
         <v>81</v>
       </c>
       <c r="H352" t="s">
-        <v>9</v>
-      </c>
-      <c r="I352" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A353">
         <v>34.4</v>
       </c>
@@ -12120,13 +10145,10 @@
         <v>81</v>
       </c>
       <c r="H353" t="s">
-        <v>9</v>
-      </c>
-      <c r="I353" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A354">
         <v>29.9</v>
       </c>
@@ -12149,13 +10171,10 @@
         <v>81</v>
       </c>
       <c r="H354" t="s">
-        <v>9</v>
-      </c>
-      <c r="I354" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A355">
         <v>33</v>
       </c>
@@ -12178,13 +10197,10 @@
         <v>81</v>
       </c>
       <c r="H355" t="s">
-        <v>30</v>
-      </c>
-      <c r="I355" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A356">
         <v>34.5</v>
       </c>
@@ -12204,13 +10220,10 @@
         <v>81</v>
       </c>
       <c r="H356" t="s">
-        <v>30</v>
-      </c>
-      <c r="I356" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A357">
         <v>33.700000000000003</v>
       </c>
@@ -12233,13 +10246,10 @@
         <v>81</v>
       </c>
       <c r="H357" t="s">
-        <v>24</v>
-      </c>
-      <c r="I357" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A358">
         <v>32.4</v>
       </c>
@@ -12262,13 +10272,10 @@
         <v>81</v>
       </c>
       <c r="H358" t="s">
-        <v>24</v>
-      </c>
-      <c r="I358" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A359">
         <v>32.9</v>
       </c>
@@ -12291,13 +10298,10 @@
         <v>81</v>
       </c>
       <c r="H359" t="s">
-        <v>24</v>
-      </c>
-      <c r="I359" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A360">
         <v>31.6</v>
       </c>
@@ -12320,13 +10324,10 @@
         <v>81</v>
       </c>
       <c r="H360" t="s">
-        <v>24</v>
-      </c>
-      <c r="I360" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A361">
         <v>28.1</v>
       </c>
@@ -12349,13 +10350,10 @@
         <v>81</v>
       </c>
       <c r="H361" t="s">
-        <v>30</v>
-      </c>
-      <c r="I361" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A362">
         <v>30.7</v>
       </c>
@@ -12378,13 +10376,10 @@
         <v>81</v>
       </c>
       <c r="H362" t="s">
-        <v>30</v>
-      </c>
-      <c r="I362" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A363">
         <v>25.4</v>
       </c>
@@ -12407,13 +10402,10 @@
         <v>81</v>
       </c>
       <c r="H363" t="s">
-        <v>24</v>
-      </c>
-      <c r="I363" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A364">
         <v>24.2</v>
       </c>
@@ -12436,13 +10428,10 @@
         <v>81</v>
       </c>
       <c r="H364" t="s">
-        <v>24</v>
-      </c>
-      <c r="I364" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A365">
         <v>22.4</v>
       </c>
@@ -12465,13 +10454,10 @@
         <v>81</v>
       </c>
       <c r="H365" t="s">
-        <v>9</v>
-      </c>
-      <c r="I365" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A366">
         <v>26.6</v>
       </c>
@@ -12494,13 +10480,10 @@
         <v>81</v>
       </c>
       <c r="H366" t="s">
-        <v>9</v>
-      </c>
-      <c r="I366" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A367">
         <v>20.2</v>
       </c>
@@ -12523,13 +10506,10 @@
         <v>81</v>
       </c>
       <c r="H367" t="s">
-        <v>9</v>
-      </c>
-      <c r="I367" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A368">
         <v>17.600000000000001</v>
       </c>
@@ -12552,13 +10532,10 @@
         <v>81</v>
       </c>
       <c r="H368" t="s">
-        <v>9</v>
-      </c>
-      <c r="I368" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A369">
         <v>28</v>
       </c>
@@ -12581,13 +10558,10 @@
         <v>82</v>
       </c>
       <c r="H369" t="s">
-        <v>9</v>
-      </c>
-      <c r="I369" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A370">
         <v>27</v>
       </c>
@@ -12610,13 +10584,10 @@
         <v>82</v>
       </c>
       <c r="H370" t="s">
-        <v>9</v>
-      </c>
-      <c r="I370" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A371">
         <v>34</v>
       </c>
@@ -12639,13 +10610,10 @@
         <v>82</v>
       </c>
       <c r="H371" t="s">
-        <v>9</v>
-      </c>
-      <c r="I371" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A372">
         <v>31</v>
       </c>
@@ -12668,13 +10636,10 @@
         <v>82</v>
       </c>
       <c r="H372" t="s">
-        <v>9</v>
-      </c>
-      <c r="I372" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A373">
         <v>29</v>
       </c>
@@ -12697,13 +10662,10 @@
         <v>82</v>
       </c>
       <c r="H373" t="s">
-        <v>9</v>
-      </c>
-      <c r="I373" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A374">
         <v>27</v>
       </c>
@@ -12726,13 +10688,10 @@
         <v>82</v>
       </c>
       <c r="H374" t="s">
-        <v>9</v>
-      </c>
-      <c r="I374" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A375">
         <v>24</v>
       </c>
@@ -12755,13 +10714,10 @@
         <v>82</v>
       </c>
       <c r="H375" t="s">
-        <v>9</v>
-      </c>
-      <c r="I375" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A376">
         <v>23</v>
       </c>
@@ -12781,13 +10737,10 @@
         <v>82</v>
       </c>
       <c r="H376" t="s">
-        <v>9</v>
-      </c>
-      <c r="I376" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A377">
         <v>36</v>
       </c>
@@ -12810,13 +10763,10 @@
         <v>82</v>
       </c>
       <c r="H377" t="s">
-        <v>30</v>
-      </c>
-      <c r="I377" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A378">
         <v>37</v>
       </c>
@@ -12839,13 +10789,10 @@
         <v>82</v>
       </c>
       <c r="H378" t="s">
-        <v>24</v>
-      </c>
-      <c r="I378" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A379">
         <v>31</v>
       </c>
@@ -12868,13 +10815,10 @@
         <v>82</v>
       </c>
       <c r="H379" t="s">
-        <v>24</v>
-      </c>
-      <c r="I379" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A380">
         <v>38</v>
       </c>
@@ -12897,13 +10841,10 @@
         <v>82</v>
       </c>
       <c r="H380" t="s">
-        <v>9</v>
-      </c>
-      <c r="I380" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A381">
         <v>36</v>
       </c>
@@ -12926,13 +10867,10 @@
         <v>82</v>
       </c>
       <c r="H381" t="s">
-        <v>9</v>
-      </c>
-      <c r="I381" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A382">
         <v>36</v>
       </c>
@@ -12955,13 +10893,10 @@
         <v>82</v>
       </c>
       <c r="H382" t="s">
-        <v>24</v>
-      </c>
-      <c r="I382" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A383">
         <v>36</v>
       </c>
@@ -12984,13 +10919,10 @@
         <v>82</v>
       </c>
       <c r="H383" t="s">
-        <v>24</v>
-      </c>
-      <c r="I383" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A384">
         <v>34</v>
       </c>
@@ -13013,13 +10945,10 @@
         <v>82</v>
       </c>
       <c r="H384" t="s">
-        <v>24</v>
-      </c>
-      <c r="I384" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A385">
         <v>38</v>
       </c>
@@ -13042,13 +10971,10 @@
         <v>82</v>
       </c>
       <c r="H385" t="s">
-        <v>24</v>
-      </c>
-      <c r="I385" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A386">
         <v>32</v>
       </c>
@@ -13071,13 +10997,10 @@
         <v>82</v>
       </c>
       <c r="H386" t="s">
-        <v>24</v>
-      </c>
-      <c r="I386" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A387">
         <v>38</v>
       </c>
@@ -13100,13 +11023,10 @@
         <v>82</v>
       </c>
       <c r="H387" t="s">
-        <v>24</v>
-      </c>
-      <c r="I387" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A388">
         <v>25</v>
       </c>
@@ -13129,13 +11049,10 @@
         <v>82</v>
       </c>
       <c r="H388" t="s">
-        <v>9</v>
-      </c>
-      <c r="I388" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A389">
         <v>38</v>
       </c>
@@ -13158,13 +11075,10 @@
         <v>82</v>
       </c>
       <c r="H389" t="s">
-        <v>9</v>
-      </c>
-      <c r="I389" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A390">
         <v>26</v>
       </c>
@@ -13187,13 +11101,10 @@
         <v>82</v>
       </c>
       <c r="H390" t="s">
-        <v>9</v>
-      </c>
-      <c r="I390" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A391">
         <v>22</v>
       </c>
@@ -13216,13 +11127,10 @@
         <v>82</v>
       </c>
       <c r="H391" t="s">
-        <v>9</v>
-      </c>
-      <c r="I391" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A392">
         <v>32</v>
       </c>
@@ -13245,13 +11153,10 @@
         <v>82</v>
       </c>
       <c r="H392" t="s">
-        <v>24</v>
-      </c>
-      <c r="I392" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A393">
         <v>36</v>
       </c>
@@ -13274,13 +11179,10 @@
         <v>82</v>
       </c>
       <c r="H393" t="s">
-        <v>9</v>
-      </c>
-      <c r="I393" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A394">
         <v>27</v>
       </c>
@@ -13303,13 +11205,10 @@
         <v>82</v>
       </c>
       <c r="H394" t="s">
-        <v>9</v>
-      </c>
-      <c r="I394" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A395">
         <v>27</v>
       </c>
@@ -13332,13 +11231,10 @@
         <v>82</v>
       </c>
       <c r="H395" t="s">
-        <v>9</v>
-      </c>
-      <c r="I395" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A396">
         <v>44</v>
       </c>
@@ -13361,13 +11257,10 @@
         <v>82</v>
       </c>
       <c r="H396" t="s">
-        <v>30</v>
-      </c>
-      <c r="I396" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A397">
         <v>32</v>
       </c>
@@ -13390,13 +11283,10 @@
         <v>82</v>
       </c>
       <c r="H397" t="s">
-        <v>9</v>
-      </c>
-      <c r="I397" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A398">
         <v>28</v>
       </c>
@@ -13419,13 +11309,10 @@
         <v>82</v>
       </c>
       <c r="H398" t="s">
-        <v>9</v>
-      </c>
-      <c r="I398" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.85">
       <c r="A399">
         <v>31</v>
       </c>
@@ -13448,10 +11335,7 @@
         <v>82</v>
       </c>
       <c r="H399" t="s">
-        <v>9</v>
-      </c>
-      <c r="I399" t="s">
-        <v>316</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -13716,20 +11600,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="37e3aeb7-4d0f-4a33-8841-3d6184eb8527" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="37e3aeb7-4d0f-4a33-8841-3d6184eb8527" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13752,14 +11636,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DD7994C-05CF-44D9-9CC3-522CCFB6C574}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F8E99D-5F8A-491F-B0EE-854194F77762}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="37e3aeb7-4d0f-4a33-8841-3d6184eb8527"/>
@@ -13774,4 +11650,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DD7994C-05CF-44D9-9CC3-522CCFB6C574}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>